--- a/corrections/corrections.xlsx
+++ b/corrections/corrections.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\carlo\Desktop\wow_vo_webui\corrections\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{784CA0AC-AC1B-4D17-8648-2FB606D3C093}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5BFC8A81-57CB-4337-86D4-B1306B145F4B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="690" uniqueCount="143">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="752" uniqueCount="168">
   <si>
     <t>source</t>
   </si>
@@ -239,9 +239,6 @@
   </si>
   <si>
     <t>furbolg_male</t>
-  </si>
-  <si>
-    <t>medivh</t>
   </si>
   <si>
     <t>none</t>
@@ -515,6 +512,110 @@
   </si>
   <si>
     <t>Greetings, adventurer; I've deciphered the Legion missive and uncovered the demons' strategic plans for this Peninsula. Apparently, there is a large group of hellish terrorfiends gathering near the Pools of Aggonar in the west. We cannot allow such a force to go unchallenged. You must go there and decimate their cursed numbers.</t>
+  </si>
+  <si>
+    <t>Ramdor? Hm, let me think; Ramdor... Oh yes, the death priest. What does he want with the book? Well it doesn't matter. Yes I lied to you and no I don't have the book. Not anymore, anyway; It was stolen, Probably by one of those filthy refugees.
+Besides, Auchindoun is now defunct. We have no use for the book; If you find it, you can keep it.
+Like I said, I saw some of those ruffians snooping around the terrace last week. Start your search with them. They're probably playing dice in the slums.</t>
+  </si>
+  <si>
+    <t>Mog'dorg wise! Him send Grok to city, look for help; Bloodmaul clan need help; Mog'dorg say, send powerful little ones to him at Blade's Edge Mountains. Him stand on tower at Circle of Blood. Mog'dorg wise!</t>
+  </si>
+  <si>
+    <t>progress</t>
+  </si>
+  <si>
+    <t>You know of the Violet Eye?  You do not look familiar.</t>
+  </si>
+  <si>
+    <t>Alturus entrusted you with this information?  That old fool;
+I suppose the damage is done, we might as well make use of you.  I suppose you will cooperate?</t>
+  </si>
+  <si>
+    <t>You fulfilled your end of the deal. I will now bind your essence to that of the dead blue dragon.
+There is an urn in the Master's Terrace, should you touch that urn, you'll now release its energy and bring life back to the charred remains of Arcanagos. Defeat the creature and retrieve its essence immediately! You will need to take it to Alturus.
+Should you fail, the stars predict you will have let a great terror loose upon the skies; A terror known as Nightbane!</t>
+  </si>
+  <si>
+    <t>The sphere; Strange; Did you know that he lived? Yes; It is here, in the sphere itself. Maimed for certain; He calls to a higher power now; No, not Illidan; Higher; Kil'jaeden the Deceiver comes; Not here; Azeroth; Unknown; Rest; Your brothers and sisters will retake Tempest Keep now.</t>
+  </si>
+  <si>
+    <t>The calming melodic tones projected by A'dal become more hushed and somber. You are shown the large naroo structure known as Tempest Keep. It is now inhabited by the forces of Kale-thoss and its power used for nefarious ends. A'dal promises you greater tasks once you've done your part to take back Tempest Keep.</t>
+  </si>
+  <si>
+    <t>Fire be witcha, mon; I see you be strong in da ways of earth already, and me thinkin' you be ready to talk to Kranal.
+Kranal live north of the Crossroads in the Barrens. He be strong in the ways of the elements and can teach ya the ways of fire; if you think you be ready.
+He be easy ta find, just don' go too far; ya go too far an' ya find yerself in da elves' lands.</t>
+  </si>
+  <si>
+    <t>Curse you!  And curse your ancestors!! Only blood and revenge can cool my rage, so if that is your wish then; do this: Throw yourself into the heart of the Skullsplitters to the east;  Slay the fiercest among them, and if you survive; then break yourself against their chief, Ana-thek the Cruel ; Hah!  Bring me his shattered armor if you can! May he tear off your limbs and leave you to rot and be eaten by carrion.</t>
+  </si>
+  <si>
+    <t>Throm-Kah, traveler! Welcome to Warsong Hold; My heart swells with pride to see that such a distinguished hero of the Horde has answered the call of duty!
+This impregnable fortress is a testament to the tenacity of the Horde. Through much we have battled to establish this foothold in Northrend. It is from here that our journey to Icecrown begins and it is through the leadership of the son of Hellscream that we will succeed!
+Garrosh awaits your arrival below; Loktaro garr!</t>
+  </si>
+  <si>
+    <t>You skim through the pages of the book, looking for anything of importance. On the last page you discover what appears to be frantic scribbling:
+Necro-lords; At least a dozen by my count; Farms to west being used as some sort of horrible spawning glade for Scourge.
+Row upon row of victims; I think they're on to me; Made a dash for the hold; I won't be captured alive.
+Dreadvenom hemotoxin; If they decide to bite into me, they'll be in for a surprise; Take this information back to Barthus.</t>
+  </si>
+  <si>
+    <t>Tanks, mon; I be talkin' bout siege machines! We got heavy tanks stationed at Garrosh's Landing on tha west coast. We gonna get you to the tank and you gonna use the tank to lay down some Horde justice on the Scourge!
+the only tricky part be getting' you there; No way we be sendin' you on our wind riders; Too risky.
+You see dat pixie o'er der; Dat blondie elf? Yanni be his name, mon; He can get you to tha coast, safely; Once there, talk to Annihilator Grek'lor!</t>
+  </si>
+  <si>
+    <t>According to Luther's notes the Scourge is now using this place as a breeding ground for those monsters you see lumbering across the field; Those monsters were once orcs; tauren.
+We need more information before a plan can be devised. I want you to investigate three sites that are heavily trafficked by Scourge: the Warsong Granary, southwest of us; Torp's Farm, directly west of us; and the old Warsong Slaughterhouse, north of us; Return to me once you've scouted 'em out.</t>
+  </si>
+  <si>
+    <t>I told them all that I remember; Why don't they believe me?
+I was gathering herbs by the rift; They came from nowhere, dark wizards with magical beasts; I was surrounded!
+A magical box appeared above me, opened up and pulled me inside. Just as it began to close around me, my rescuers swooped in on the backs of red drakes; It was breathtaking!
+I never thanked them for saving me; Please adventurer, find them and pass on my gratitude.</t>
+  </si>
+  <si>
+    <t>Lovely! Just lovely! Hrmph; I don't understand; Unless; Why of course!</t>
+  </si>
+  <si>
+    <t>AHa; Look at that!</t>
+  </si>
+  <si>
+    <t>Hiss! … Have you come to mock me, traveler?</t>
+  </si>
+  <si>
+    <t>Your efforts against the Nerubians have given us a reprieve from the overwhelming Scourge assault. Thanks to your accomplishments, we can strike at the Scourge fortress to the northeast without fear of attack from the west.
+As for the horn, I will safeguard it until next we need its power. Stormhoof gave his life to secure the horn and we cannot suffer its loss again.</t>
+  </si>
+  <si>
+    <t>Strewn across this beach amidst the flotsam and jetsam, are crates and sacks of animal parts. It would seem that Nesingwary is in cahoots with the Northsea Freebooters. Those dirty pirates are transporting the goods that Nesingwary's murderous lackeys gather offshore. No doubt they will end up in the homes and on the backs of wealthy, unscrupulous individuals across Azeroth.
+This won't happen; Not on our watch; Bring me all shipments that you find upon this beach; They'll never have them!</t>
+  </si>
+  <si>
+    <t>The key is forged anew.
+Now heed my counsel, traveler. Succeed in your endeavor or die trying; for if a single scale falls from one of my drakes I shall hold you personally accountable; Now, off with you.</t>
+  </si>
+  <si>
+    <t>Greetings, traveler; I am Garren of Dalaran; 
+Not long ago, the rift was a peaceful place; geothermally speaking at least.
+Recently though, earthquakes have occurred with alarming frequency and scars in the earth have appeared, exposing unique energy fields of chaotic power.
+My mission here is to chart and monitor these anomalies. My instruments indicate that another has appeared on the cliff face to the southwest.
+Take this device with you and use it when you locate the new disruption.</t>
+  </si>
+  <si>
+    <t>The frivolous games you play here are of no consequence; You and your Dalaran allies pick at loose threads while the fabric of this world's future is being shredded.
+Still, this may provide my drakes some needed amusement; Show me this key.</t>
+  </si>
+  <si>
+    <t>This is it; the key is ours!</t>
+  </si>
+  <si>
+    <t>murloc</t>
+  </si>
+  <si>
+    <t>wind_elemental</t>
   </si>
 </sst>
 </file>
@@ -557,7 +658,17 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="7">
+  <dxfs count="8">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -904,7 +1015,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{56545B79-22C0-4057-A076-1E697524330B}">
-  <dimension ref="A1:F1110"/>
+  <dimension ref="A1:F1138"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -4713,51 +4824,51 @@
     </row>
     <row r="475" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A475" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B475">
         <v>9538</v>
       </c>
       <c r="D475" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="476" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A476" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B476">
         <v>10428</v>
       </c>
       <c r="D476" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="477" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A477" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B477">
         <v>9539</v>
       </c>
       <c r="D477" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="478" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A478" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B478">
         <v>9540</v>
       </c>
       <c r="D478" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="479" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A479" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B479">
         <v>6564</v>
@@ -4768,7 +4879,7 @@
     </row>
     <row r="480" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A480" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B480">
         <v>9438</v>
@@ -4779,62 +4890,62 @@
     </row>
     <row r="481" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A481" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B481">
         <v>10294</v>
       </c>
       <c r="D481" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="482" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A482" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B482">
         <v>10838</v>
       </c>
       <c r="D482" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="483" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A483" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B483">
         <v>9820</v>
       </c>
       <c r="D483" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="484" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A484" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B484">
         <v>10210</v>
       </c>
       <c r="D484" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="485" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A485" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B485">
         <v>9544</v>
       </c>
       <c r="D485" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="486" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A486" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B486">
         <v>9576</v>
@@ -4848,134 +4959,134 @@
     </row>
     <row r="487" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A487" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B487">
         <v>10216</v>
       </c>
       <c r="D487" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="488" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A488" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B488">
         <v>10845</v>
       </c>
       <c r="D488" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="489" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A489" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B489">
         <v>9870</v>
       </c>
       <c r="D489" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="490" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A490" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B490">
         <v>9859</v>
       </c>
       <c r="D490" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="491" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A491" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B491">
         <v>9865</v>
       </c>
       <c r="D491" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="492" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A492" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B492">
         <v>10134</v>
       </c>
       <c r="D492" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="493" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A493" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B493">
         <v>9636</v>
       </c>
       <c r="D493" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="494" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A494" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B494">
         <v>9923</v>
       </c>
       <c r="D494" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="495" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A495" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B495">
         <v>9869</v>
       </c>
       <c r="D495" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="496" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A496" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B496">
         <v>10009</v>
       </c>
       <c r="D496" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="497" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A497" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B497">
         <v>10010</v>
       </c>
       <c r="D497" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="498" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A498" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B498">
         <v>10703</v>
       </c>
       <c r="D498" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="499" spans="1:5" x14ac:dyDescent="0.25">
@@ -5020,7 +5131,7 @@
     </row>
     <row r="504" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A504" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B504">
         <v>831</v>
@@ -5031,7 +5142,7 @@
     </row>
     <row r="505" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A505" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B505">
         <v>831</v>
@@ -5098,7 +5209,7 @@
     </row>
     <row r="513" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A513" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B513">
         <v>1393</v>
@@ -9634,79 +9745,79 @@
     </row>
     <row r="1080" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1080" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B1080">
         <v>10958</v>
       </c>
       <c r="D1080" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="1081" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1081" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B1081">
         <v>10806</v>
       </c>
       <c r="D1081" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="1082" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1082" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B1082">
         <v>10191</v>
       </c>
       <c r="D1082" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="1083" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1083" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B1083">
         <v>10191</v>
       </c>
       <c r="D1083" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="1084" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1084" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B1084">
         <v>9541</v>
       </c>
       <c r="D1084" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="1085" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1085" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B1085">
         <v>9542</v>
       </c>
       <c r="D1085" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="1086" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1086" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B1086">
         <v>1003</v>
       </c>
       <c r="D1086" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="1087" spans="1:5" x14ac:dyDescent="0.25">
@@ -9719,46 +9830,46 @@
     </row>
     <row r="1088" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1088" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B1088">
         <v>663</v>
       </c>
       <c r="D1088" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="1089" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1089" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B1089">
         <v>488</v>
       </c>
       <c r="D1089" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="1090" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1090" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B1090">
         <v>488</v>
       </c>
       <c r="D1090" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="1091" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1091" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B1091">
         <v>489</v>
       </c>
       <c r="D1091" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="1092" spans="1:5" x14ac:dyDescent="0.25">
@@ -9787,87 +9898,87 @@
     </row>
     <row r="1095" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1095" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B1095">
         <v>7728</v>
       </c>
       <c r="D1095" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="1096" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1096" t="s">
+        <v>124</v>
+      </c>
+      <c r="D1096" t="s">
         <v>125</v>
-      </c>
-      <c r="D1096" t="s">
-        <v>126</v>
       </c>
     </row>
     <row r="1097" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1097" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B1097">
         <v>4501</v>
       </c>
       <c r="D1097" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="1098" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1098" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B1098">
         <v>4022</v>
       </c>
       <c r="D1098" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="1099" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1099" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B1099">
         <v>8479</v>
       </c>
       <c r="D1099" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="1100" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1100" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B1100">
         <v>8479</v>
       </c>
       <c r="D1100" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="1101" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1101" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B1101">
         <v>477</v>
       </c>
       <c r="D1101" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="1102" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1102" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B1102">
         <v>1058</v>
       </c>
       <c r="D1102" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="1103" spans="1:5" x14ac:dyDescent="0.25">
@@ -9880,90 +9991,398 @@
     </row>
     <row r="1104" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1104" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B1104">
         <v>12720</v>
       </c>
       <c r="D1104" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="1105" spans="1:4" x14ac:dyDescent="0.25">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="1105" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1105" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B1105">
         <v>8054</v>
       </c>
-      <c r="D1105" s="1" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="1106" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="D1105" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="1106" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1106" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B1106">
         <v>645</v>
       </c>
-      <c r="D1106" s="1" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="1107" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="D1106" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="1107" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1107" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B1107">
         <v>646</v>
       </c>
-      <c r="D1107" s="1" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="1108" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="D1107" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="1108" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1108" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B1108">
         <v>10390</v>
       </c>
-      <c r="D1108" s="1" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="1109" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="D1108" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="1109" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1109" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B1109">
         <v>10392</v>
       </c>
-      <c r="D1109" s="1" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="1110" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="D1109" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="1110" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1110" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B1110">
         <v>10389</v>
       </c>
-      <c r="D1110" s="1" t="s">
+      <c r="D1110" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="1111" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1111" t="s">
+        <v>87</v>
+      </c>
+      <c r="B1111">
+        <v>10231</v>
+      </c>
+      <c r="D1111" t="s">
         <v>142</v>
+      </c>
+    </row>
+    <row r="1112" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1112" t="s">
+        <v>87</v>
+      </c>
+      <c r="B1112">
+        <v>10983</v>
+      </c>
+      <c r="D1112" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="1113" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1113" t="s">
+        <v>144</v>
+      </c>
+      <c r="B1113">
+        <v>9826</v>
+      </c>
+      <c r="D1113" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="1114" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1114" t="s">
+        <v>85</v>
+      </c>
+      <c r="B1114">
+        <v>9826</v>
+      </c>
+      <c r="D1114" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="1115" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1115" t="s">
+        <v>87</v>
+      </c>
+      <c r="B1115">
+        <v>349</v>
+      </c>
+      <c r="E1115">
+        <v>-77</v>
+      </c>
+    </row>
+    <row r="1116" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1116" t="s">
+        <v>87</v>
+      </c>
+      <c r="B1116">
+        <v>9644</v>
+      </c>
+      <c r="D1116" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="1117" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1117" t="s">
+        <v>85</v>
+      </c>
+      <c r="B1117">
+        <v>11007</v>
+      </c>
+      <c r="D1117" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="1118" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1118" t="s">
+        <v>87</v>
+      </c>
+      <c r="B1118">
+        <v>10560</v>
+      </c>
+      <c r="D1118" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="1119" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1119" t="s">
+        <v>87</v>
+      </c>
+      <c r="B1119">
+        <v>1522</v>
+      </c>
+      <c r="D1119" s="1" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="1120" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1120" t="s">
+        <v>87</v>
+      </c>
+      <c r="B1120">
+        <v>586</v>
+      </c>
+      <c r="D1120" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="F1120" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="1121" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1121" t="s">
+        <v>85</v>
+      </c>
+      <c r="B1121">
+        <v>586</v>
+      </c>
+      <c r="F1121" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="1122" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B1122">
+        <v>585</v>
+      </c>
+      <c r="F1122" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="1123" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1123" t="s">
+        <v>87</v>
+      </c>
+      <c r="B1123">
+        <v>588</v>
+      </c>
+      <c r="F1123" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="1124" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1124" t="s">
+        <v>87</v>
+      </c>
+      <c r="B1124">
+        <v>1261</v>
+      </c>
+      <c r="F1124" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="1125" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1125" t="s">
+        <v>87</v>
+      </c>
+      <c r="B1125">
+        <v>11585</v>
+      </c>
+      <c r="D1125" s="1" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="1126" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1126" t="s">
+        <v>87</v>
+      </c>
+      <c r="B1126">
+        <v>11615</v>
+      </c>
+      <c r="D1126" s="1" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="1127" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1127" t="s">
+        <v>87</v>
+      </c>
+      <c r="B1127">
+        <v>11636</v>
+      </c>
+      <c r="D1127" s="1" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="1128" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1128" t="s">
+        <v>87</v>
+      </c>
+      <c r="B1128">
+        <v>11686</v>
+      </c>
+      <c r="D1128" s="1" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="1129" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1129" t="s">
+        <v>87</v>
+      </c>
+      <c r="B1129">
+        <v>11574</v>
+      </c>
+      <c r="D1129" s="1" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="1130" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1130" t="s">
+        <v>85</v>
+      </c>
+      <c r="B1130">
+        <v>11716</v>
+      </c>
+      <c r="D1130" s="1" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="1131" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1131" t="s">
+        <v>85</v>
+      </c>
+      <c r="B1131">
+        <v>11717</v>
+      </c>
+      <c r="D1131" s="1" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="1132" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1132" t="s">
+        <v>85</v>
+      </c>
+      <c r="B1132">
+        <v>11620</v>
+      </c>
+      <c r="D1132" s="1" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="1133" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1133" t="s">
+        <v>85</v>
+      </c>
+      <c r="B1133">
+        <v>11706</v>
+      </c>
+      <c r="D1133" s="1" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="1134" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1134" t="s">
+        <v>87</v>
+      </c>
+      <c r="B1134">
+        <v>11871</v>
+      </c>
+      <c r="D1134" s="1" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="1135" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1135" t="s">
+        <v>87</v>
+      </c>
+      <c r="B1135">
+        <v>11680</v>
+      </c>
+      <c r="D1135" s="1" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="1136" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1136" t="s">
+        <v>87</v>
+      </c>
+      <c r="B1136">
+        <v>11576</v>
+      </c>
+      <c r="D1136" s="1" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="1137" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1137" t="s">
+        <v>85</v>
+      </c>
+      <c r="B1137">
+        <v>11679</v>
+      </c>
+      <c r="D1137" s="1" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="1138" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1138" t="s">
+        <v>85</v>
+      </c>
+      <c r="B1138">
+        <v>11680</v>
+      </c>
+      <c r="D1138" s="1" t="s">
+        <v>165</v>
       </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="B1">
-    <cfRule type="duplicateValues" dxfId="6" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="7" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B59:B113 B17:B57">
-    <cfRule type="duplicateValues" dxfId="5" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="6" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B1085:B1088 B486:B1083 B2:B484">
-    <cfRule type="duplicateValues" dxfId="4" priority="96"/>
+    <cfRule type="duplicateValues" dxfId="5" priority="96"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -9971,7 +10390,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3D60A7C4-82C4-4AAF-A00A-127D625F91A3}">
-  <dimension ref="A1:H734"/>
+  <dimension ref="A1:H742"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -9997,7 +10416,7 @@
         <v>6</v>
       </c>
       <c r="H1" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
@@ -10005,7 +10424,7 @@
         <v>22264</v>
       </c>
       <c r="E2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
@@ -10013,7 +10432,7 @@
         <v>22271</v>
       </c>
       <c r="E3" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
@@ -10505,7 +10924,7 @@
         <v>23233</v>
       </c>
       <c r="E45" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.25">
@@ -11270,7 +11689,7 @@
         <v>22941</v>
       </c>
       <c r="E135" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="136" spans="1:5" x14ac:dyDescent="0.25">
@@ -11286,7 +11705,7 @@
         <v>23253</v>
       </c>
       <c r="E137" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="138" spans="1:5" x14ac:dyDescent="0.25">
@@ -11302,7 +11721,7 @@
         <v>23316</v>
       </c>
       <c r="E139" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="140" spans="1:5" x14ac:dyDescent="0.25">
@@ -11420,7 +11839,7 @@
         <v>24729</v>
       </c>
       <c r="E153" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="154" spans="1:5" x14ac:dyDescent="0.25">
@@ -11463,7 +11882,7 @@
         <v>25205</v>
       </c>
       <c r="E158" t="s">
-        <v>53</v>
+        <v>166</v>
       </c>
     </row>
     <row r="159" spans="1:5" x14ac:dyDescent="0.25">
@@ -11487,7 +11906,7 @@
         <v>25208</v>
       </c>
       <c r="E161" t="s">
-        <v>53</v>
+        <v>166</v>
       </c>
     </row>
     <row r="162" spans="1:5" x14ac:dyDescent="0.25">
@@ -11503,7 +11922,7 @@
         <v>25376</v>
       </c>
       <c r="E163" t="s">
-        <v>36</v>
+        <v>167</v>
       </c>
     </row>
     <row r="164" spans="1:5" x14ac:dyDescent="0.25">
@@ -11543,7 +11962,7 @@
         <v>25862</v>
       </c>
       <c r="E168" t="s">
-        <v>36</v>
+        <v>66</v>
       </c>
     </row>
     <row r="169" spans="1:5" x14ac:dyDescent="0.25">
@@ -11551,7 +11970,7 @@
         <v>25812</v>
       </c>
       <c r="E169" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
     </row>
     <row r="170" spans="1:5" x14ac:dyDescent="0.25">
@@ -11879,7 +12298,7 @@
         <v>28658</v>
       </c>
       <c r="E210" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="211" spans="1:5" x14ac:dyDescent="0.25">
@@ -11919,7 +12338,7 @@
         <v>28910</v>
       </c>
       <c r="E215" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="216" spans="1:5" x14ac:dyDescent="0.25">
@@ -12567,15 +12986,15 @@
     </row>
     <row r="296" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A296">
-        <v>17468</v>
+        <v>17114</v>
       </c>
       <c r="E296" t="s">
-        <v>21</v>
+        <v>70</v>
       </c>
     </row>
     <row r="297" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A297">
-        <v>17114</v>
+        <v>17442</v>
       </c>
       <c r="E297" t="s">
         <v>70</v>
@@ -12583,7 +13002,7 @@
     </row>
     <row r="298" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A298">
-        <v>17442</v>
+        <v>17441</v>
       </c>
       <c r="E298" t="s">
         <v>70</v>
@@ -12591,7 +13010,7 @@
     </row>
     <row r="299" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A299">
-        <v>17441</v>
+        <v>17440</v>
       </c>
       <c r="E299" t="s">
         <v>70</v>
@@ -12599,7 +13018,7 @@
     </row>
     <row r="300" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A300">
-        <v>17440</v>
+        <v>17443</v>
       </c>
       <c r="E300" t="s">
         <v>70</v>
@@ -12607,7 +13026,7 @@
     </row>
     <row r="301" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A301">
-        <v>17443</v>
+        <v>17445</v>
       </c>
       <c r="E301" t="s">
         <v>70</v>
@@ -12615,7 +13034,7 @@
     </row>
     <row r="302" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A302">
-        <v>17445</v>
+        <v>17682</v>
       </c>
       <c r="E302" t="s">
         <v>70</v>
@@ -12623,23 +13042,23 @@
     </row>
     <row r="303" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A303">
-        <v>17682</v>
+        <v>17712</v>
       </c>
       <c r="E303" t="s">
-        <v>70</v>
+        <v>136</v>
       </c>
     </row>
     <row r="304" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A304">
-        <v>17712</v>
+        <v>17856</v>
       </c>
       <c r="E304" t="s">
-        <v>33</v>
+        <v>53</v>
       </c>
     </row>
     <row r="305" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A305">
-        <v>17856</v>
+        <v>17857</v>
       </c>
       <c r="E305" t="s">
         <v>53</v>
@@ -12647,7 +13066,7 @@
     </row>
     <row r="306" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A306">
-        <v>17857</v>
+        <v>17866</v>
       </c>
       <c r="E306" t="s">
         <v>53</v>
@@ -12655,23 +13074,23 @@
     </row>
     <row r="307" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A307">
-        <v>17866</v>
+        <v>17877</v>
       </c>
       <c r="E307" t="s">
-        <v>53</v>
+        <v>133</v>
       </c>
     </row>
     <row r="308" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A308">
-        <v>17877</v>
+        <v>17923</v>
       </c>
       <c r="E308" t="s">
-        <v>134</v>
+        <v>53</v>
       </c>
     </row>
     <row r="309" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A309">
-        <v>17923</v>
+        <v>17925</v>
       </c>
       <c r="E309" t="s">
         <v>53</v>
@@ -12679,7 +13098,7 @@
     </row>
     <row r="310" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A310">
-        <v>17925</v>
+        <v>17924</v>
       </c>
       <c r="E310" t="s">
         <v>53</v>
@@ -12687,47 +13106,47 @@
     </row>
     <row r="311" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A311">
-        <v>17924</v>
+        <v>18099</v>
       </c>
       <c r="E311" t="s">
-        <v>53</v>
+        <v>41</v>
       </c>
     </row>
     <row r="312" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A312">
-        <v>18099</v>
+        <v>15608</v>
       </c>
       <c r="E312" t="s">
-        <v>41</v>
+        <v>83</v>
       </c>
     </row>
     <row r="313" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A313">
-        <v>15608</v>
+        <v>18265</v>
       </c>
       <c r="E313" t="s">
-        <v>71</v>
+        <v>48</v>
       </c>
     </row>
     <row r="314" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A314">
-        <v>18265</v>
+        <v>18262</v>
       </c>
       <c r="E314" t="s">
-        <v>48</v>
+        <v>11</v>
       </c>
     </row>
     <row r="315" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A315">
-        <v>18262</v>
+        <v>18276</v>
       </c>
       <c r="E315" t="s">
-        <v>11</v>
+        <v>48</v>
       </c>
     </row>
     <row r="316" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A316">
-        <v>18276</v>
+        <v>18335</v>
       </c>
       <c r="E316" t="s">
         <v>48</v>
@@ -12735,7 +13154,7 @@
     </row>
     <row r="317" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A317">
-        <v>18335</v>
+        <v>18333</v>
       </c>
       <c r="E317" t="s">
         <v>48</v>
@@ -12743,23 +13162,23 @@
     </row>
     <row r="318" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A318">
-        <v>18333</v>
+        <v>19456</v>
       </c>
       <c r="E318" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
     </row>
     <row r="319" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A319">
-        <v>19456</v>
+        <v>22293</v>
       </c>
       <c r="E319" t="s">
-        <v>41</v>
+        <v>12</v>
       </c>
     </row>
     <row r="320" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A320">
-        <v>22293</v>
+        <v>20206</v>
       </c>
       <c r="E320" t="s">
         <v>12</v>
@@ -12767,39 +13186,39 @@
     </row>
     <row r="321" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A321">
-        <v>20206</v>
+        <v>22823</v>
       </c>
       <c r="E321" t="s">
-        <v>12</v>
+        <v>53</v>
       </c>
     </row>
     <row r="322" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A322">
-        <v>22823</v>
+        <v>22836</v>
       </c>
       <c r="E322" t="s">
-        <v>53</v>
+        <v>20</v>
       </c>
     </row>
     <row r="323" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A323">
-        <v>22836</v>
+        <v>23428</v>
       </c>
       <c r="E323" t="s">
-        <v>20</v>
+        <v>82</v>
       </c>
     </row>
     <row r="324" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A324">
-        <v>23428</v>
+        <v>23462</v>
       </c>
       <c r="E324" t="s">
-        <v>83</v>
+        <v>49</v>
       </c>
     </row>
     <row r="325" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A325">
-        <v>23462</v>
+        <v>23464</v>
       </c>
       <c r="E325" t="s">
         <v>49</v>
@@ -12807,7 +13226,7 @@
     </row>
     <row r="326" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A326">
-        <v>23464</v>
+        <v>23463</v>
       </c>
       <c r="E326" t="s">
         <v>49</v>
@@ -12815,7 +13234,7 @@
     </row>
     <row r="327" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A327">
-        <v>23463</v>
+        <v>23461</v>
       </c>
       <c r="E327" t="s">
         <v>49</v>
@@ -12823,7 +13242,7 @@
     </row>
     <row r="328" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A328">
-        <v>23461</v>
+        <v>23466</v>
       </c>
       <c r="E328" t="s">
         <v>49</v>
@@ -12831,7 +13250,7 @@
     </row>
     <row r="329" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A329">
-        <v>23466</v>
+        <v>23465</v>
       </c>
       <c r="E329" t="s">
         <v>49</v>
@@ -12839,23 +13258,23 @@
     </row>
     <row r="330" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A330">
-        <v>23465</v>
+        <v>25206</v>
       </c>
       <c r="E330" t="s">
-        <v>49</v>
+        <v>166</v>
       </c>
     </row>
     <row r="331" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A331">
-        <v>25206</v>
+        <v>26401</v>
       </c>
       <c r="E331" t="s">
-        <v>61</v>
+        <v>36</v>
       </c>
     </row>
     <row r="332" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A332">
-        <v>26401</v>
+        <v>26520</v>
       </c>
       <c r="E332" t="s">
         <v>36</v>
@@ -12863,63 +13282,63 @@
     </row>
     <row r="333" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A333">
-        <v>26520</v>
+        <v>26371</v>
       </c>
       <c r="E333" t="s">
-        <v>36</v>
+        <v>20</v>
       </c>
     </row>
     <row r="334" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A334">
-        <v>26371</v>
+        <v>27646</v>
       </c>
       <c r="E334" t="s">
-        <v>20</v>
+        <v>42</v>
       </c>
     </row>
     <row r="335" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A335">
-        <v>27646</v>
+        <v>28106</v>
       </c>
       <c r="E335" t="s">
-        <v>42</v>
+        <v>61</v>
       </c>
     </row>
     <row r="336" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A336">
-        <v>28106</v>
+        <v>28107</v>
       </c>
       <c r="E336" t="s">
-        <v>61</v>
+        <v>53</v>
       </c>
     </row>
     <row r="337" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A337">
-        <v>28107</v>
+        <v>30997</v>
       </c>
       <c r="E337" t="s">
-        <v>53</v>
+        <v>60</v>
       </c>
     </row>
     <row r="338" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A338">
-        <v>30997</v>
+        <v>31868</v>
       </c>
       <c r="E338" t="s">
-        <v>60</v>
+        <v>12</v>
       </c>
     </row>
     <row r="339" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A339">
-        <v>31868</v>
+        <v>32594</v>
       </c>
       <c r="E339" t="s">
-        <v>12</v>
+        <v>66</v>
       </c>
     </row>
     <row r="340" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A340">
-        <v>32594</v>
+        <v>32540</v>
       </c>
       <c r="E340" t="s">
         <v>66</v>
@@ -12927,55 +13346,55 @@
     </row>
     <row r="341" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A341">
-        <v>32540</v>
+        <v>37221</v>
       </c>
       <c r="E341" t="s">
-        <v>66</v>
+        <v>45</v>
       </c>
     </row>
     <row r="342" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A342">
-        <v>37221</v>
+        <v>37223</v>
       </c>
       <c r="E342" t="s">
-        <v>45</v>
+        <v>35</v>
       </c>
     </row>
     <row r="343" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A343">
-        <v>37223</v>
+        <v>17085</v>
       </c>
       <c r="E343" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="344" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A344">
-        <v>17085</v>
+        <v>18803</v>
       </c>
       <c r="E344" t="s">
-        <v>36</v>
+        <v>70</v>
       </c>
     </row>
     <row r="345" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A345">
-        <v>18803</v>
+        <v>16075</v>
       </c>
       <c r="E345" t="s">
-        <v>70</v>
+        <v>17</v>
       </c>
     </row>
     <row r="346" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A346">
-        <v>16075</v>
+        <v>28518</v>
       </c>
       <c r="E346" t="s">
-        <v>17</v>
+        <v>44</v>
       </c>
     </row>
     <row r="347" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A347">
-        <v>28518</v>
+        <v>28444</v>
       </c>
       <c r="E347" t="s">
         <v>44</v>
@@ -12983,7 +13402,7 @@
     </row>
     <row r="348" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A348">
-        <v>28444</v>
+        <v>29173</v>
       </c>
       <c r="E348" t="s">
         <v>44</v>
@@ -12991,7 +13410,7 @@
     </row>
     <row r="349" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A349">
-        <v>29173</v>
+        <v>31084</v>
       </c>
       <c r="E349" t="s">
         <v>44</v>
@@ -12999,7 +13418,7 @@
     </row>
     <row r="350" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A350">
-        <v>31084</v>
+        <v>37120</v>
       </c>
       <c r="E350" t="s">
         <v>44</v>
@@ -13007,15 +13426,15 @@
     </row>
     <row r="351" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A351">
-        <v>37120</v>
+        <v>29396</v>
       </c>
       <c r="E351" t="s">
-        <v>44</v>
+        <v>72</v>
       </c>
     </row>
     <row r="352" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A352">
-        <v>29396</v>
+        <v>29405</v>
       </c>
       <c r="E352" t="s">
         <v>73</v>
@@ -13023,15 +13442,15 @@
     </row>
     <row r="353" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A353">
-        <v>29405</v>
+        <v>33769</v>
       </c>
       <c r="E353" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="354" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A354">
-        <v>33769</v>
+        <v>28532</v>
       </c>
       <c r="E354" t="s">
         <v>74</v>
@@ -13039,7 +13458,7 @@
     </row>
     <row r="355" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A355">
-        <v>28532</v>
+        <v>29804</v>
       </c>
       <c r="E355" t="s">
         <v>75</v>
@@ -13047,23 +13466,23 @@
     </row>
     <row r="356" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A356">
-        <v>29804</v>
+        <v>30002</v>
       </c>
       <c r="E356" t="s">
-        <v>76</v>
+        <v>44</v>
       </c>
     </row>
     <row r="357" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A357">
-        <v>30002</v>
+        <v>30946</v>
       </c>
       <c r="E357" t="s">
-        <v>44</v>
+        <v>75</v>
       </c>
     </row>
     <row r="358" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A358">
-        <v>30946</v>
+        <v>33762</v>
       </c>
       <c r="E358" t="s">
         <v>76</v>
@@ -13071,7 +13490,7 @@
     </row>
     <row r="359" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A359">
-        <v>33762</v>
+        <v>30056</v>
       </c>
       <c r="E359" t="s">
         <v>77</v>
@@ -13079,7 +13498,7 @@
     </row>
     <row r="360" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A360">
-        <v>30056</v>
+        <v>33770</v>
       </c>
       <c r="E360" t="s">
         <v>78</v>
@@ -13087,23 +13506,23 @@
     </row>
     <row r="361" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A361">
-        <v>33770</v>
+        <v>29343</v>
       </c>
       <c r="E361" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
     </row>
     <row r="362" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A362">
-        <v>29343</v>
+        <v>29344</v>
       </c>
       <c r="E362" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
     </row>
     <row r="363" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A363">
-        <v>29344</v>
+        <v>29456</v>
       </c>
       <c r="E363" t="s">
         <v>80</v>
@@ -13111,175 +13530,175 @@
     </row>
     <row r="364" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A364">
-        <v>29456</v>
+        <v>29560</v>
       </c>
       <c r="E364" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="365" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A365">
-        <v>29560</v>
+        <v>30218</v>
       </c>
       <c r="E365" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
     </row>
     <row r="366" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A366">
-        <v>30218</v>
+        <v>30596</v>
       </c>
       <c r="E366" t="s">
-        <v>78</v>
+        <v>44</v>
       </c>
     </row>
     <row r="367" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A367">
-        <v>30596</v>
+        <v>30631</v>
       </c>
       <c r="E367" t="s">
-        <v>44</v>
+        <v>81</v>
       </c>
     </row>
     <row r="368" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A368">
-        <v>30631</v>
+        <v>30944</v>
       </c>
       <c r="E368" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
     </row>
     <row r="369" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A369">
-        <v>30944</v>
+        <v>38194</v>
       </c>
       <c r="E369" t="s">
-        <v>80</v>
+        <v>44</v>
       </c>
     </row>
     <row r="370" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A370">
-        <v>38194</v>
+        <v>392</v>
       </c>
       <c r="E370" t="s">
-        <v>44</v>
+        <v>33</v>
       </c>
     </row>
     <row r="371" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A371">
-        <v>392</v>
+        <v>302</v>
       </c>
       <c r="E371" t="s">
-        <v>33</v>
+        <v>58</v>
       </c>
     </row>
     <row r="372" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A372">
-        <v>302</v>
+        <v>23256</v>
       </c>
       <c r="E372" t="s">
-        <v>58</v>
+        <v>82</v>
       </c>
     </row>
     <row r="373" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A373">
-        <v>23256</v>
+        <v>22266</v>
       </c>
       <c r="E373" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="374" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A374">
-        <v>22266</v>
+        <v>23110</v>
       </c>
       <c r="E374" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="375" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A375">
-        <v>23110</v>
+        <v>23362</v>
       </c>
       <c r="E375" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="376" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A376">
-        <v>23362</v>
+        <v>23365</v>
       </c>
       <c r="E376" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="377" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A377">
-        <v>23365</v>
+        <v>23115</v>
       </c>
       <c r="E377" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="378" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A378">
-        <v>23115</v>
+        <v>23347</v>
       </c>
       <c r="E378" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="379" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A379">
-        <v>23347</v>
+        <v>22270</v>
       </c>
       <c r="E379" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="380" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A380">
-        <v>22270</v>
+        <v>23112</v>
       </c>
       <c r="E380" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="381" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A381">
-        <v>23112</v>
-      </c>
-      <c r="E381" t="s">
-        <v>83</v>
+        <v>20735</v>
+      </c>
+      <c r="B381">
+        <v>2</v>
       </c>
     </row>
     <row r="382" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A382">
-        <v>20735</v>
+        <v>3230</v>
       </c>
       <c r="B382">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="383" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A383">
-        <v>3230</v>
+        <v>16128</v>
       </c>
       <c r="B383">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="384" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A384">
-        <v>16128</v>
+        <v>23843</v>
       </c>
       <c r="B384">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="385" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A385">
-        <v>23843</v>
+        <v>23835</v>
       </c>
       <c r="B385">
         <v>1</v>
@@ -13287,7 +13706,7 @@
     </row>
     <row r="386" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A386">
-        <v>23835</v>
+        <v>24393</v>
       </c>
       <c r="B386">
         <v>1</v>
@@ -13295,7 +13714,7 @@
     </row>
     <row r="387" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A387">
-        <v>24393</v>
+        <v>25233</v>
       </c>
       <c r="B387">
         <v>1</v>
@@ -13303,15 +13722,18 @@
     </row>
     <row r="388" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A388">
-        <v>25233</v>
+        <v>25580</v>
       </c>
       <c r="B388">
         <v>1</v>
+      </c>
+      <c r="E388" t="s">
+        <v>136</v>
       </c>
     </row>
     <row r="389" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A389">
-        <v>25580</v>
+        <v>26719</v>
       </c>
       <c r="B389">
         <v>1</v>
@@ -13319,31 +13741,31 @@
     </row>
     <row r="390" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A390">
-        <v>26719</v>
-      </c>
-      <c r="B390">
-        <v>1</v>
+        <v>620</v>
+      </c>
+      <c r="E390" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="391" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A391">
-        <v>620</v>
+        <v>1244</v>
       </c>
       <c r="E391" t="s">
-        <v>12</v>
+        <v>41</v>
       </c>
     </row>
     <row r="392" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A392">
-        <v>1244</v>
+        <v>2227</v>
       </c>
       <c r="E392" t="s">
-        <v>41</v>
+        <v>58</v>
       </c>
     </row>
     <row r="393" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A393">
-        <v>2227</v>
+        <v>2278</v>
       </c>
       <c r="E393" t="s">
         <v>58</v>
@@ -13351,95 +13773,95 @@
     </row>
     <row r="394" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A394">
-        <v>2278</v>
+        <v>2425</v>
       </c>
       <c r="E394" t="s">
-        <v>58</v>
+        <v>36</v>
       </c>
     </row>
     <row r="395" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A395">
-        <v>2425</v>
+        <v>2500</v>
       </c>
       <c r="E395" t="s">
-        <v>36</v>
+        <v>136</v>
       </c>
     </row>
     <row r="396" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A396">
-        <v>2500</v>
+        <v>2546</v>
       </c>
       <c r="E396" t="s">
-        <v>33</v>
+        <v>136</v>
       </c>
     </row>
     <row r="397" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A397">
-        <v>2546</v>
+        <v>2610</v>
       </c>
       <c r="E397" t="s">
-        <v>33</v>
+        <v>136</v>
       </c>
     </row>
     <row r="398" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A398">
-        <v>2610</v>
+        <v>2766</v>
       </c>
       <c r="E398" t="s">
-        <v>137</v>
+        <v>11</v>
       </c>
     </row>
     <row r="399" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A399">
-        <v>2766</v>
+        <v>3430</v>
       </c>
       <c r="E399" t="s">
-        <v>11</v>
+        <v>70</v>
       </c>
     </row>
     <row r="400" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A400">
-        <v>3430</v>
+        <v>3439</v>
       </c>
       <c r="E400" t="s">
-        <v>70</v>
+        <v>17</v>
       </c>
     </row>
     <row r="401" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A401">
-        <v>3439</v>
+        <v>3568</v>
       </c>
       <c r="E401" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
     </row>
     <row r="402" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A402">
-        <v>3568</v>
+        <v>3584</v>
       </c>
       <c r="E402" t="s">
-        <v>12</v>
+        <v>40</v>
       </c>
     </row>
     <row r="403" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A403">
-        <v>3584</v>
+        <v>3897</v>
       </c>
       <c r="E403" t="s">
-        <v>40</v>
+        <v>70</v>
       </c>
     </row>
     <row r="404" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A404">
-        <v>3897</v>
+        <v>3901</v>
       </c>
       <c r="E404" t="s">
-        <v>70</v>
+        <v>40</v>
       </c>
     </row>
     <row r="405" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A405">
-        <v>3901</v>
+        <v>3916</v>
       </c>
       <c r="E405" t="s">
         <v>40</v>
@@ -13447,7 +13869,7 @@
     </row>
     <row r="406" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A406">
-        <v>3916</v>
+        <v>3920</v>
       </c>
       <c r="E406" t="s">
         <v>40</v>
@@ -13455,23 +13877,23 @@
     </row>
     <row r="407" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A407">
-        <v>3920</v>
+        <v>3994</v>
       </c>
       <c r="E407" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
     </row>
     <row r="408" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A408">
-        <v>3994</v>
+        <v>4500</v>
       </c>
       <c r="E408" t="s">
-        <v>46</v>
+        <v>11</v>
       </c>
     </row>
     <row r="409" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A409">
-        <v>4500</v>
+        <v>4501</v>
       </c>
       <c r="E409" t="s">
         <v>11</v>
@@ -13479,7 +13901,7 @@
     </row>
     <row r="410" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A410">
-        <v>4501</v>
+        <v>4502</v>
       </c>
       <c r="E410" t="s">
         <v>11</v>
@@ -13487,7 +13909,7 @@
     </row>
     <row r="411" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A411">
-        <v>4502</v>
+        <v>4503</v>
       </c>
       <c r="E411" t="s">
         <v>11</v>
@@ -13495,31 +13917,31 @@
     </row>
     <row r="412" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A412">
-        <v>4503</v>
+        <v>4606</v>
       </c>
       <c r="E412" t="s">
-        <v>11</v>
+        <v>58</v>
       </c>
     </row>
     <row r="413" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A413">
-        <v>4606</v>
+        <v>4982</v>
       </c>
       <c r="E413" t="s">
-        <v>58</v>
+        <v>20</v>
       </c>
     </row>
     <row r="414" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A414">
-        <v>4982</v>
+        <v>4983</v>
       </c>
       <c r="E414" t="s">
-        <v>20</v>
+        <v>11</v>
       </c>
     </row>
     <row r="415" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A415">
-        <v>4983</v>
+        <v>5087</v>
       </c>
       <c r="E415" t="s">
         <v>11</v>
@@ -13527,31 +13949,31 @@
     </row>
     <row r="416" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A416">
-        <v>5087</v>
+        <v>5397</v>
       </c>
       <c r="E416" t="s">
-        <v>11</v>
+        <v>32</v>
       </c>
     </row>
     <row r="417" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A417">
-        <v>5397</v>
+        <v>5398</v>
       </c>
       <c r="E417" t="s">
-        <v>32</v>
+        <v>133</v>
       </c>
     </row>
     <row r="418" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A418">
-        <v>5398</v>
+        <v>5891</v>
       </c>
       <c r="E418" t="s">
-        <v>134</v>
+        <v>41</v>
       </c>
     </row>
     <row r="419" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A419">
-        <v>5891</v>
+        <v>5895</v>
       </c>
       <c r="E419" t="s">
         <v>41</v>
@@ -13559,47 +13981,47 @@
     </row>
     <row r="420" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A420">
-        <v>5895</v>
+        <v>5955</v>
       </c>
       <c r="E420" t="s">
-        <v>41</v>
+        <v>66</v>
       </c>
     </row>
     <row r="421" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A421">
-        <v>5955</v>
+        <v>6134</v>
       </c>
       <c r="E421" t="s">
-        <v>66</v>
+        <v>36</v>
       </c>
     </row>
     <row r="422" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A422">
-        <v>6134</v>
+        <v>7363</v>
       </c>
       <c r="E422" t="s">
-        <v>36</v>
+        <v>22</v>
       </c>
     </row>
     <row r="423" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A423">
-        <v>7363</v>
+        <v>7765</v>
       </c>
       <c r="E423" t="s">
-        <v>22</v>
+        <v>41</v>
       </c>
     </row>
     <row r="424" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A424">
-        <v>7765</v>
+        <v>7784</v>
       </c>
       <c r="E424" t="s">
-        <v>41</v>
+        <v>12</v>
       </c>
     </row>
     <row r="425" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A425">
-        <v>7784</v>
+        <v>7806</v>
       </c>
       <c r="E425" t="s">
         <v>12</v>
@@ -13607,7 +14029,7 @@
     </row>
     <row r="426" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A426">
-        <v>7806</v>
+        <v>7807</v>
       </c>
       <c r="E426" t="s">
         <v>12</v>
@@ -13615,127 +14037,127 @@
     </row>
     <row r="427" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A427">
-        <v>7807</v>
+        <v>7918</v>
       </c>
       <c r="E427" t="s">
-        <v>12</v>
+        <v>68</v>
       </c>
     </row>
     <row r="428" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A428">
-        <v>7918</v>
+        <v>8405</v>
       </c>
       <c r="E428" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="429" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A429">
-        <v>8405</v>
+        <v>9459</v>
       </c>
       <c r="E429" t="s">
-        <v>70</v>
+        <v>49</v>
       </c>
     </row>
     <row r="430" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A430">
-        <v>9459</v>
+        <v>9500</v>
       </c>
       <c r="E430" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="431" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A431">
-        <v>9500</v>
+        <v>9516</v>
       </c>
       <c r="E431" t="s">
-        <v>50</v>
+        <v>36</v>
       </c>
     </row>
     <row r="432" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A432">
-        <v>9516</v>
+        <v>9598</v>
       </c>
       <c r="E432" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
     </row>
     <row r="433" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A433">
-        <v>9598</v>
+        <v>9623</v>
       </c>
       <c r="E433" t="s">
-        <v>41</v>
+        <v>12</v>
       </c>
     </row>
     <row r="434" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A434">
-        <v>9623</v>
+        <v>10321</v>
       </c>
       <c r="E434" t="s">
-        <v>12</v>
+        <v>49</v>
       </c>
     </row>
     <row r="435" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A435">
-        <v>10321</v>
+        <v>10666</v>
       </c>
       <c r="E435" t="s">
-        <v>49</v>
+        <v>11</v>
       </c>
     </row>
     <row r="436" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A436">
-        <v>10666</v>
+        <v>10684</v>
       </c>
       <c r="E436" t="s">
-        <v>11</v>
+        <v>58</v>
       </c>
     </row>
     <row r="437" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A437">
-        <v>10684</v>
+        <v>10740</v>
       </c>
       <c r="E437" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
     </row>
     <row r="438" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A438">
-        <v>10740</v>
+        <v>10799</v>
       </c>
       <c r="E438" t="s">
-        <v>53</v>
+        <v>70</v>
       </c>
     </row>
     <row r="439" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A439">
-        <v>10799</v>
+        <v>10918</v>
       </c>
       <c r="E439" t="s">
-        <v>70</v>
+        <v>39</v>
       </c>
     </row>
     <row r="440" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A440">
-        <v>10918</v>
+        <v>10926</v>
       </c>
       <c r="E440" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
     </row>
     <row r="441" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A441">
-        <v>10926</v>
+        <v>11554</v>
       </c>
       <c r="E441" t="s">
-        <v>42</v>
+        <v>70</v>
       </c>
     </row>
     <row r="442" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A442">
-        <v>11554</v>
+        <v>11555</v>
       </c>
       <c r="E442" t="s">
         <v>70</v>
@@ -13743,7 +14165,7 @@
     </row>
     <row r="443" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A443">
-        <v>11555</v>
+        <v>11556</v>
       </c>
       <c r="E443" t="s">
         <v>70</v>
@@ -13751,7 +14173,7 @@
     </row>
     <row r="444" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A444">
-        <v>11556</v>
+        <v>11557</v>
       </c>
       <c r="E444" t="s">
         <v>70</v>
@@ -13759,119 +14181,119 @@
     </row>
     <row r="445" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A445">
-        <v>11557</v>
+        <v>11862</v>
       </c>
       <c r="E445" t="s">
-        <v>70</v>
+        <v>36</v>
       </c>
     </row>
     <row r="446" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A446">
-        <v>11862</v>
+        <v>13020</v>
       </c>
       <c r="E446" t="s">
-        <v>36</v>
+        <v>49</v>
       </c>
     </row>
     <row r="447" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A447">
-        <v>13020</v>
+        <v>13278</v>
       </c>
       <c r="E447" t="s">
-        <v>49</v>
+        <v>36</v>
       </c>
     </row>
     <row r="448" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A448">
-        <v>13278</v>
+        <v>13636</v>
       </c>
       <c r="E448" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
     </row>
     <row r="449" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A449">
-        <v>13636</v>
+        <v>13697</v>
       </c>
       <c r="E449" t="s">
-        <v>17</v>
+        <v>40</v>
       </c>
     </row>
     <row r="450" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A450">
-        <v>13697</v>
+        <v>13698</v>
       </c>
       <c r="E450" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
     </row>
     <row r="451" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A451">
-        <v>13698</v>
+        <v>13699</v>
       </c>
       <c r="E451" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
     </row>
     <row r="452" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A452">
-        <v>13699</v>
+        <v>13716</v>
       </c>
       <c r="E452" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
     </row>
     <row r="453" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A453">
-        <v>13716</v>
+        <v>13717</v>
       </c>
       <c r="E453" t="s">
-        <v>46</v>
+        <v>108</v>
       </c>
     </row>
     <row r="454" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A454">
-        <v>13717</v>
+        <v>14305</v>
       </c>
       <c r="E454" t="s">
-        <v>109</v>
+        <v>20</v>
       </c>
     </row>
     <row r="455" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A455">
-        <v>14305</v>
+        <v>14325</v>
       </c>
       <c r="E455" t="s">
-        <v>20</v>
+        <v>11</v>
       </c>
     </row>
     <row r="456" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A456">
-        <v>14325</v>
+        <v>14444</v>
       </c>
       <c r="E456" t="s">
-        <v>11</v>
+        <v>20</v>
       </c>
     </row>
     <row r="457" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A457">
-        <v>14444</v>
+        <v>14470</v>
       </c>
       <c r="E457" t="s">
-        <v>20</v>
+        <v>31</v>
       </c>
     </row>
     <row r="458" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A458">
-        <v>14470</v>
+        <v>14524</v>
       </c>
       <c r="E458" t="s">
-        <v>31</v>
+        <v>41</v>
       </c>
     </row>
     <row r="459" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A459">
-        <v>14524</v>
+        <v>14525</v>
       </c>
       <c r="E459" t="s">
         <v>41</v>
@@ -13879,7 +14301,7 @@
     </row>
     <row r="460" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A460">
-        <v>14525</v>
+        <v>14526</v>
       </c>
       <c r="E460" t="s">
         <v>41</v>
@@ -13887,119 +14309,119 @@
     </row>
     <row r="461" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A461">
-        <v>14526</v>
+        <v>14566</v>
       </c>
       <c r="E461" t="s">
-        <v>41</v>
+        <v>12</v>
       </c>
     </row>
     <row r="462" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A462">
-        <v>14566</v>
+        <v>14731</v>
       </c>
       <c r="E462" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="463" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A463">
-        <v>14731</v>
+        <v>14902</v>
       </c>
       <c r="E463" t="s">
-        <v>11</v>
+        <v>34</v>
       </c>
     </row>
     <row r="464" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A464">
-        <v>14902</v>
+        <v>15069</v>
       </c>
       <c r="E464" t="s">
-        <v>34</v>
+        <v>12</v>
       </c>
     </row>
     <row r="465" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A465">
-        <v>15069</v>
+        <v>15192</v>
       </c>
       <c r="E465" t="s">
-        <v>12</v>
+        <v>49</v>
       </c>
     </row>
     <row r="466" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A466">
-        <v>15192</v>
+        <v>1733</v>
       </c>
       <c r="E466" t="s">
-        <v>49</v>
+        <v>20</v>
       </c>
     </row>
     <row r="467" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A467">
-        <v>1733</v>
+        <v>2230</v>
       </c>
       <c r="E467" t="s">
-        <v>20</v>
+        <v>53</v>
       </c>
     </row>
     <row r="468" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A468">
-        <v>2230</v>
+        <v>2274</v>
       </c>
       <c r="E468" t="s">
-        <v>53</v>
+        <v>12</v>
       </c>
     </row>
     <row r="469" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A469">
-        <v>2274</v>
+        <v>3585</v>
       </c>
       <c r="E469" t="s">
-        <v>12</v>
+        <v>40</v>
       </c>
     </row>
     <row r="470" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A470">
-        <v>3585</v>
+        <v>6015</v>
       </c>
       <c r="E470" t="s">
-        <v>40</v>
+        <v>67</v>
       </c>
     </row>
     <row r="471" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A471">
-        <v>6015</v>
+        <v>9274</v>
       </c>
       <c r="E471" t="s">
-        <v>67</v>
+        <v>12</v>
       </c>
     </row>
     <row r="472" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A472">
-        <v>9274</v>
+        <v>11558</v>
       </c>
       <c r="E472" t="s">
-        <v>12</v>
+        <v>70</v>
       </c>
     </row>
     <row r="473" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A473">
-        <v>11558</v>
+        <v>14322</v>
       </c>
       <c r="E473" t="s">
-        <v>70</v>
+        <v>11</v>
       </c>
     </row>
     <row r="474" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A474">
-        <v>14322</v>
+        <v>14504</v>
       </c>
       <c r="E474" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="475" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A475">
-        <v>14504</v>
+        <v>14568</v>
       </c>
       <c r="E475" t="s">
         <v>12</v>
@@ -14007,55 +14429,55 @@
     </row>
     <row r="476" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A476">
-        <v>14568</v>
+        <v>15079</v>
       </c>
       <c r="E476" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
     </row>
     <row r="477" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A477">
-        <v>15079</v>
+        <v>28357</v>
       </c>
       <c r="E477" t="s">
-        <v>29</v>
+        <v>44</v>
       </c>
     </row>
     <row r="478" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A478">
-        <v>28357</v>
+        <v>16721</v>
       </c>
       <c r="E478" t="s">
-        <v>44</v>
+        <v>30</v>
       </c>
     </row>
     <row r="479" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A479">
-        <v>16721</v>
+        <v>22013</v>
       </c>
       <c r="E479" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
     </row>
     <row r="480" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A480">
-        <v>22013</v>
-      </c>
-      <c r="E480" t="s">
-        <v>21</v>
+        <v>25223</v>
+      </c>
+      <c r="B480">
+        <v>1</v>
       </c>
     </row>
     <row r="481" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A481">
-        <v>25223</v>
+        <v>16305</v>
       </c>
       <c r="B481">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="482" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A482">
-        <v>16305</v>
+        <v>16303</v>
       </c>
       <c r="B482">
         <v>0</v>
@@ -14063,7 +14485,7 @@
     </row>
     <row r="483" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A483">
-        <v>16303</v>
+        <v>16304</v>
       </c>
       <c r="B483">
         <v>0</v>
@@ -14071,7 +14493,7 @@
     </row>
     <row r="484" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A484">
-        <v>16304</v>
+        <v>13435</v>
       </c>
       <c r="B484">
         <v>0</v>
@@ -14079,7 +14501,7 @@
     </row>
     <row r="485" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A485">
-        <v>13435</v>
+        <v>20805</v>
       </c>
       <c r="B485">
         <v>0</v>
@@ -14087,7 +14509,7 @@
     </row>
     <row r="486" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A486">
-        <v>20805</v>
+        <v>20310</v>
       </c>
       <c r="B486">
         <v>0</v>
@@ -14095,7 +14517,7 @@
     </row>
     <row r="487" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A487">
-        <v>20310</v>
+        <v>16408</v>
       </c>
       <c r="B487">
         <v>0</v>
@@ -14103,26 +14525,26 @@
     </row>
     <row r="488" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A488">
-        <v>16408</v>
+        <v>17008</v>
       </c>
       <c r="B488">
         <v>0</v>
+      </c>
+      <c r="E488" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="489" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A489">
-        <v>17008</v>
+        <v>17125</v>
       </c>
       <c r="B489">
         <v>0</v>
-      </c>
-      <c r="E489" t="s">
-        <v>18</v>
       </c>
     </row>
     <row r="490" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A490">
-        <v>17125</v>
+        <v>16782</v>
       </c>
       <c r="B490">
         <v>0</v>
@@ -14130,23 +14552,23 @@
     </row>
     <row r="491" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A491">
-        <v>16782</v>
+        <v>18589</v>
       </c>
       <c r="B491">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="492" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A492">
-        <v>18589</v>
+        <v>15306</v>
       </c>
       <c r="B492">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="493" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A493">
-        <v>15306</v>
+        <v>15282</v>
       </c>
       <c r="B493">
         <v>0</v>
@@ -14154,7 +14576,7 @@
     </row>
     <row r="494" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A494">
-        <v>15282</v>
+        <v>16133</v>
       </c>
       <c r="B494">
         <v>0</v>
@@ -14162,7 +14584,7 @@
     </row>
     <row r="495" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A495">
-        <v>16133</v>
+        <v>16112</v>
       </c>
       <c r="B495">
         <v>0</v>
@@ -14170,7 +14592,7 @@
     </row>
     <row r="496" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A496">
-        <v>16112</v>
+        <v>16376</v>
       </c>
       <c r="B496">
         <v>0</v>
@@ -14178,7 +14600,7 @@
     </row>
     <row r="497" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A497">
-        <v>16376</v>
+        <v>16399</v>
       </c>
       <c r="B497">
         <v>0</v>
@@ -14186,7 +14608,7 @@
     </row>
     <row r="498" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A498">
-        <v>16399</v>
+        <v>16478</v>
       </c>
       <c r="B498">
         <v>0</v>
@@ -14194,7 +14616,7 @@
     </row>
     <row r="499" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A499">
-        <v>16478</v>
+        <v>16495</v>
       </c>
       <c r="B499">
         <v>0</v>
@@ -14202,7 +14624,7 @@
     </row>
     <row r="500" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A500">
-        <v>16495</v>
+        <v>16788</v>
       </c>
       <c r="B500">
         <v>0</v>
@@ -14210,7 +14632,7 @@
     </row>
     <row r="501" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A501">
-        <v>16788</v>
+        <v>16113</v>
       </c>
       <c r="B501">
         <v>0</v>
@@ -14218,47 +14640,47 @@
     </row>
     <row r="502" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A502">
-        <v>16113</v>
-      </c>
-      <c r="B502">
-        <v>0</v>
+        <v>28510</v>
+      </c>
+      <c r="E502" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="503" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A503">
-        <v>28510</v>
+        <v>28647</v>
       </c>
       <c r="E503" t="s">
-        <v>76</v>
+        <v>43</v>
       </c>
     </row>
     <row r="504" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A504">
-        <v>28647</v>
+        <v>28919</v>
       </c>
       <c r="E504" t="s">
-        <v>43</v>
+        <v>83</v>
       </c>
     </row>
     <row r="505" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A505">
-        <v>28919</v>
+        <v>27928</v>
       </c>
       <c r="E505" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
     </row>
     <row r="506" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A506">
-        <v>27928</v>
+        <v>26170</v>
       </c>
       <c r="E506" t="s">
-        <v>79</v>
+        <v>44</v>
       </c>
     </row>
     <row r="507" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A507">
-        <v>26170</v>
+        <v>28913</v>
       </c>
       <c r="E507" t="s">
         <v>44</v>
@@ -14266,55 +14688,55 @@
     </row>
     <row r="508" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A508">
-        <v>28913</v>
+        <v>28914</v>
       </c>
       <c r="E508" t="s">
-        <v>44</v>
+        <v>63</v>
       </c>
     </row>
     <row r="509" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A509">
-        <v>28914</v>
+        <v>28912</v>
       </c>
       <c r="E509" t="s">
-        <v>63</v>
+        <v>75</v>
       </c>
     </row>
     <row r="510" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A510">
-        <v>28912</v>
+        <v>29053</v>
       </c>
       <c r="E510" t="s">
-        <v>76</v>
+        <v>84</v>
       </c>
     </row>
     <row r="511" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A511">
-        <v>29053</v>
+        <v>28472</v>
       </c>
       <c r="E511" t="s">
-        <v>85</v>
+        <v>63</v>
       </c>
     </row>
     <row r="512" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A512">
-        <v>28472</v>
+        <v>31082</v>
       </c>
       <c r="E512" t="s">
-        <v>63</v>
+        <v>75</v>
       </c>
     </row>
     <row r="513" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A513">
-        <v>31082</v>
-      </c>
-      <c r="E513" t="s">
-        <v>76</v>
+        <v>16786</v>
+      </c>
+      <c r="B513">
+        <v>0</v>
       </c>
     </row>
     <row r="514" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A514">
-        <v>16786</v>
+        <v>16787</v>
       </c>
       <c r="B514">
         <v>0</v>
@@ -14322,15 +14744,15 @@
     </row>
     <row r="515" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A515">
-        <v>16787</v>
+        <v>25169</v>
       </c>
       <c r="B515">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="516" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A516">
-        <v>25169</v>
+        <v>187236</v>
       </c>
       <c r="B516">
         <v>1</v>
@@ -14338,15 +14760,15 @@
     </row>
     <row r="517" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A517">
-        <v>187236</v>
+        <v>15723</v>
       </c>
       <c r="B517">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="518" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A518">
-        <v>15723</v>
+        <v>15707</v>
       </c>
       <c r="B518">
         <v>0</v>
@@ -14354,7 +14776,7 @@
     </row>
     <row r="519" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A519">
-        <v>15707</v>
+        <v>15702</v>
       </c>
       <c r="B519">
         <v>0</v>
@@ -14362,7 +14784,7 @@
     </row>
     <row r="520" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A520">
-        <v>15702</v>
+        <v>15529</v>
       </c>
       <c r="B520">
         <v>0</v>
@@ -14370,7 +14792,7 @@
     </row>
     <row r="521" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A521">
-        <v>15529</v>
+        <v>15528</v>
       </c>
       <c r="B521">
         <v>0</v>
@@ -14378,7 +14800,7 @@
     </row>
     <row r="522" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A522">
-        <v>15528</v>
+        <v>15522</v>
       </c>
       <c r="B522">
         <v>0</v>
@@ -14386,7 +14808,7 @@
     </row>
     <row r="523" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A523">
-        <v>15522</v>
+        <v>15477</v>
       </c>
       <c r="B523">
         <v>0</v>
@@ -14394,7 +14816,7 @@
     </row>
     <row r="524" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A524">
-        <v>15477</v>
+        <v>15448</v>
       </c>
       <c r="B524">
         <v>0</v>
@@ -14402,7 +14824,7 @@
     </row>
     <row r="525" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A525">
-        <v>15448</v>
+        <v>15446</v>
       </c>
       <c r="B525">
         <v>0</v>
@@ -14410,7 +14832,7 @@
     </row>
     <row r="526" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A526">
-        <v>15446</v>
+        <v>20460</v>
       </c>
       <c r="B526">
         <v>0</v>
@@ -14418,221 +14840,221 @@
     </row>
     <row r="527" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A527">
-        <v>20460</v>
+        <v>24132</v>
       </c>
       <c r="B527">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="528" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A528">
-        <v>24132</v>
-      </c>
-      <c r="B528">
-        <v>1</v>
+        <v>19937</v>
+      </c>
+      <c r="C528">
+        <v>1</v>
+      </c>
+      <c r="D528">
+        <v>0</v>
+      </c>
+      <c r="E528" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="529" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A529">
-        <v>19937</v>
-      </c>
-      <c r="C529">
-        <v>1</v>
-      </c>
-      <c r="D529">
-        <v>0</v>
+        <v>38609</v>
       </c>
       <c r="E529" t="s">
-        <v>13</v>
+        <v>35</v>
       </c>
     </row>
     <row r="530" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A530">
-        <v>16161</v>
-      </c>
-      <c r="B530">
-        <v>0</v>
+        <v>38606</v>
+      </c>
+      <c r="E530" t="s">
+        <v>45</v>
       </c>
     </row>
     <row r="531" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A531">
-        <v>38609</v>
+        <v>1747</v>
       </c>
       <c r="E531" t="s">
-        <v>35</v>
+        <v>20</v>
       </c>
     </row>
     <row r="532" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A532">
-        <v>38606</v>
+        <v>3467</v>
       </c>
       <c r="E532" t="s">
-        <v>45</v>
+        <v>33</v>
       </c>
     </row>
     <row r="533" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A533">
-        <v>1747</v>
+        <v>4566</v>
       </c>
       <c r="E533" t="s">
-        <v>20</v>
+        <v>58</v>
       </c>
     </row>
     <row r="534" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A534">
-        <v>3467</v>
+        <v>5624</v>
       </c>
       <c r="E534" t="s">
-        <v>33</v>
+        <v>11</v>
       </c>
     </row>
     <row r="535" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A535">
-        <v>4566</v>
+        <v>6109</v>
       </c>
       <c r="E535" t="s">
-        <v>58</v>
+        <v>49</v>
       </c>
     </row>
     <row r="536" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A536">
-        <v>5624</v>
+        <v>6669</v>
       </c>
       <c r="E536" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="537" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A537">
-        <v>6109</v>
+        <v>7166</v>
       </c>
       <c r="E537" t="s">
-        <v>49</v>
+        <v>12</v>
       </c>
     </row>
     <row r="538" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A538">
-        <v>6669</v>
+        <v>7172</v>
       </c>
       <c r="E538" t="s">
-        <v>12</v>
+        <v>68</v>
       </c>
     </row>
     <row r="539" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A539">
-        <v>7166</v>
+        <v>8441</v>
       </c>
       <c r="E539" t="s">
-        <v>12</v>
+        <v>36</v>
       </c>
     </row>
     <row r="540" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A540">
-        <v>7172</v>
+        <v>8612</v>
       </c>
       <c r="E540" t="s">
-        <v>68</v>
+        <v>12</v>
       </c>
     </row>
     <row r="541" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A541">
-        <v>8441</v>
+        <v>8767</v>
       </c>
       <c r="E541" t="s">
-        <v>36</v>
+        <v>11</v>
       </c>
     </row>
     <row r="542" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A542">
-        <v>8612</v>
+        <v>8816</v>
       </c>
       <c r="E542" t="s">
-        <v>12</v>
+        <v>36</v>
       </c>
     </row>
     <row r="543" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A543">
-        <v>8767</v>
+        <v>9502</v>
       </c>
       <c r="E543" t="s">
-        <v>11</v>
+        <v>29</v>
       </c>
     </row>
     <row r="544" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A544">
-        <v>8816</v>
+        <v>10432</v>
       </c>
       <c r="E544" t="s">
-        <v>36</v>
+        <v>83</v>
       </c>
     </row>
     <row r="545" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A545">
-        <v>9502</v>
+        <v>10475</v>
       </c>
       <c r="E545" t="s">
-        <v>29</v>
+        <v>83</v>
       </c>
     </row>
     <row r="546" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A546">
-        <v>10432</v>
+        <v>11441</v>
       </c>
       <c r="E546" t="s">
-        <v>84</v>
+        <v>11</v>
       </c>
     </row>
     <row r="547" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A547">
-        <v>10475</v>
+        <v>11444</v>
       </c>
       <c r="E547" t="s">
-        <v>84</v>
+        <v>11</v>
       </c>
     </row>
     <row r="548" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A548">
-        <v>11441</v>
+        <v>11491</v>
       </c>
       <c r="E548" t="s">
-        <v>11</v>
+        <v>41</v>
       </c>
     </row>
     <row r="549" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A549">
-        <v>11444</v>
+        <v>11956</v>
       </c>
       <c r="E549" t="s">
-        <v>11</v>
+        <v>46</v>
       </c>
     </row>
     <row r="550" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A550">
-        <v>11491</v>
+        <v>12144</v>
       </c>
       <c r="E550" t="s">
-        <v>41</v>
+        <v>12</v>
       </c>
     </row>
     <row r="551" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A551">
-        <v>11956</v>
+        <v>14321</v>
       </c>
       <c r="E551" t="s">
-        <v>46</v>
+        <v>11</v>
       </c>
     </row>
     <row r="552" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A552">
-        <v>12144</v>
+        <v>14323</v>
       </c>
       <c r="E552" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="553" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A553">
-        <v>14321</v>
+        <v>14324</v>
       </c>
       <c r="E553" t="s">
         <v>11</v>
@@ -14640,7 +15062,7 @@
     </row>
     <row r="554" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A554">
-        <v>14323</v>
+        <v>14326</v>
       </c>
       <c r="E554" t="s">
         <v>11</v>
@@ -14648,7 +15070,7 @@
     </row>
     <row r="555" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A555">
-        <v>14324</v>
+        <v>14353</v>
       </c>
       <c r="E555" t="s">
         <v>11</v>
@@ -14656,82 +15078,82 @@
     </row>
     <row r="556" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A556">
-        <v>14326</v>
+        <v>15481</v>
       </c>
       <c r="E556" t="s">
-        <v>11</v>
+        <v>49</v>
       </c>
     </row>
     <row r="557" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A557">
-        <v>14353</v>
+        <v>16015</v>
+      </c>
+      <c r="B557">
+        <v>0</v>
       </c>
       <c r="E557" t="s">
-        <v>11</v>
+        <v>31</v>
       </c>
     </row>
     <row r="558" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A558">
-        <v>15481</v>
+        <v>16221</v>
       </c>
       <c r="E558" t="s">
-        <v>49</v>
+        <v>23</v>
       </c>
     </row>
     <row r="559" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A559">
-        <v>16015</v>
-      </c>
-      <c r="B559">
-        <v>0</v>
+        <v>17772</v>
       </c>
       <c r="E559" t="s">
-        <v>31</v>
+        <v>45</v>
       </c>
     </row>
     <row r="560" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A560">
-        <v>16221</v>
+        <v>17764</v>
       </c>
       <c r="E560" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
     </row>
     <row r="561" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A561">
-        <v>17772</v>
+        <v>18197</v>
       </c>
       <c r="E561" t="s">
-        <v>45</v>
+        <v>22</v>
       </c>
     </row>
     <row r="562" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A562">
-        <v>17764</v>
+        <v>18351</v>
       </c>
       <c r="E562" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="563" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A563">
-        <v>18197</v>
+        <v>19669</v>
       </c>
       <c r="E563" t="s">
-        <v>22</v>
+        <v>48</v>
       </c>
     </row>
     <row r="564" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A564">
-        <v>18351</v>
+        <v>19676</v>
       </c>
       <c r="E564" t="s">
-        <v>11</v>
+        <v>48</v>
       </c>
     </row>
     <row r="565" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A565">
-        <v>19669</v>
+        <v>19679</v>
       </c>
       <c r="E565" t="s">
         <v>48</v>
@@ -14739,15 +15161,15 @@
     </row>
     <row r="566" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A566">
-        <v>19676</v>
+        <v>20082</v>
       </c>
       <c r="E566" t="s">
-        <v>48</v>
+        <v>19</v>
       </c>
     </row>
     <row r="567" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A567">
-        <v>19679</v>
+        <v>20194</v>
       </c>
       <c r="E567" t="s">
         <v>48</v>
@@ -14755,71 +15177,71 @@
     </row>
     <row r="568" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A568">
-        <v>20082</v>
+        <v>20985</v>
       </c>
       <c r="E568" t="s">
-        <v>19</v>
+        <v>48</v>
       </c>
     </row>
     <row r="569" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A569">
-        <v>20194</v>
+        <v>22932</v>
       </c>
       <c r="E569" t="s">
-        <v>48</v>
+        <v>31</v>
       </c>
     </row>
     <row r="570" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A570">
-        <v>20985</v>
+        <v>23052</v>
       </c>
       <c r="E570" t="s">
-        <v>48</v>
+        <v>11</v>
       </c>
     </row>
     <row r="571" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A571">
-        <v>22932</v>
+        <v>23050</v>
       </c>
       <c r="E571" t="s">
-        <v>31</v>
+        <v>20</v>
       </c>
     </row>
     <row r="572" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A572">
-        <v>23052</v>
+        <v>23089</v>
       </c>
       <c r="E572" t="s">
-        <v>11</v>
+        <v>22</v>
       </c>
     </row>
     <row r="573" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A573">
-        <v>23050</v>
+        <v>23191</v>
       </c>
       <c r="E573" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="574" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A574">
-        <v>23089</v>
+        <v>28615</v>
       </c>
       <c r="E574" t="s">
-        <v>22</v>
+        <v>31</v>
       </c>
     </row>
     <row r="575" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A575">
-        <v>23191</v>
+        <v>29480</v>
       </c>
       <c r="E575" t="s">
-        <v>22</v>
+        <v>31</v>
       </c>
     </row>
     <row r="576" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A576">
-        <v>28615</v>
+        <v>31078</v>
       </c>
       <c r="E576" t="s">
         <v>31</v>
@@ -14827,15 +15249,15 @@
     </row>
     <row r="577" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A577">
-        <v>29480</v>
+        <v>16222</v>
       </c>
       <c r="E577" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
     </row>
     <row r="578" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A578">
-        <v>31078</v>
+        <v>18956</v>
       </c>
       <c r="E578" t="s">
         <v>31</v>
@@ -14843,87 +15265,87 @@
     </row>
     <row r="579" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A579">
-        <v>16222</v>
+        <v>18568</v>
       </c>
       <c r="E579" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
     </row>
     <row r="580" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A580">
-        <v>18956</v>
+        <v>17900</v>
       </c>
       <c r="E580" t="s">
-        <v>31</v>
+        <v>41</v>
       </c>
     </row>
     <row r="581" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A581">
-        <v>18568</v>
+        <v>17901</v>
       </c>
       <c r="E581" t="s">
-        <v>29</v>
+        <v>41</v>
       </c>
     </row>
     <row r="582" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A582">
-        <v>17900</v>
+        <v>35594</v>
       </c>
       <c r="E582" t="s">
-        <v>41</v>
+        <v>29</v>
       </c>
     </row>
     <row r="583" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A583">
-        <v>17901</v>
+        <v>18588</v>
       </c>
       <c r="E583" t="s">
-        <v>41</v>
+        <v>31</v>
       </c>
     </row>
     <row r="584" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A584">
-        <v>35594</v>
+        <v>18585</v>
       </c>
       <c r="E584" t="s">
-        <v>29</v>
+        <v>11</v>
       </c>
     </row>
     <row r="585" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A585">
-        <v>18588</v>
+        <v>18252</v>
       </c>
       <c r="E585" t="s">
-        <v>31</v>
+        <v>52</v>
       </c>
     </row>
     <row r="586" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A586">
-        <v>18585</v>
-      </c>
-      <c r="E586" t="s">
-        <v>11</v>
+        <v>31239</v>
+      </c>
+      <c r="B586">
+        <v>1</v>
       </c>
     </row>
     <row r="587" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A587">
-        <v>18252</v>
+        <v>21183</v>
       </c>
       <c r="E587" t="s">
-        <v>52</v>
+        <v>108</v>
       </c>
     </row>
     <row r="588" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A588">
-        <v>31239</v>
-      </c>
-      <c r="B588">
-        <v>1</v>
+        <v>21685</v>
+      </c>
+      <c r="E588" t="s">
+        <v>108</v>
       </c>
     </row>
     <row r="589" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A589">
-        <v>21183</v>
+        <v>16841</v>
       </c>
       <c r="E589" t="s">
         <v>109</v>
@@ -14931,31 +15353,31 @@
     </row>
     <row r="590" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A590">
-        <v>21685</v>
-      </c>
-      <c r="E590" t="s">
-        <v>109</v>
+        <v>16285</v>
+      </c>
+      <c r="B590">
+        <v>0</v>
       </c>
     </row>
     <row r="591" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A591">
-        <v>16841</v>
-      </c>
-      <c r="E591" t="s">
-        <v>110</v>
+        <v>24965</v>
+      </c>
+      <c r="B591">
+        <v>1</v>
       </c>
     </row>
     <row r="592" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A592">
-        <v>16285</v>
+        <v>25037</v>
       </c>
       <c r="B592">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="593" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A593">
-        <v>24965</v>
+        <v>25950</v>
       </c>
       <c r="B593">
         <v>1</v>
@@ -14963,7 +15385,7 @@
     </row>
     <row r="594" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A594">
-        <v>25037</v>
+        <v>25036</v>
       </c>
       <c r="B594">
         <v>1</v>
@@ -14971,7 +15393,7 @@
     </row>
     <row r="595" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A595">
-        <v>25950</v>
+        <v>25133</v>
       </c>
       <c r="B595">
         <v>1</v>
@@ -14979,7 +15401,7 @@
     </row>
     <row r="596" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A596">
-        <v>25036</v>
+        <v>25061</v>
       </c>
       <c r="B596">
         <v>1</v>
@@ -14987,7 +15409,7 @@
     </row>
     <row r="597" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A597">
-        <v>25133</v>
+        <v>25057</v>
       </c>
       <c r="B597">
         <v>1</v>
@@ -14995,7 +15417,7 @@
     </row>
     <row r="598" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A598">
-        <v>25061</v>
+        <v>25167</v>
       </c>
       <c r="B598">
         <v>1</v>
@@ -15003,7 +15425,7 @@
     </row>
     <row r="599" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A599">
-        <v>25057</v>
+        <v>24932</v>
       </c>
       <c r="B599">
         <v>1</v>
@@ -15011,7 +15433,7 @@
     </row>
     <row r="600" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A600">
-        <v>25167</v>
+        <v>25034</v>
       </c>
       <c r="B600">
         <v>1</v>
@@ -15019,7 +15441,7 @@
     </row>
     <row r="601" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A601">
-        <v>24932</v>
+        <v>25112</v>
       </c>
       <c r="B601">
         <v>1</v>
@@ -15027,7 +15449,7 @@
     </row>
     <row r="602" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A602">
-        <v>25034</v>
+        <v>25069</v>
       </c>
       <c r="B602">
         <v>1</v>
@@ -15035,7 +15457,7 @@
     </row>
     <row r="603" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A603">
-        <v>25112</v>
+        <v>25108</v>
       </c>
       <c r="B603">
         <v>1</v>
@@ -15043,7 +15465,7 @@
     </row>
     <row r="604" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A604">
-        <v>25069</v>
+        <v>25046</v>
       </c>
       <c r="B604">
         <v>1</v>
@@ -15051,7 +15473,7 @@
     </row>
     <row r="605" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A605">
-        <v>25108</v>
+        <v>25319</v>
       </c>
       <c r="B605">
         <v>1</v>
@@ -15059,7 +15481,7 @@
     </row>
     <row r="606" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A606">
-        <v>25046</v>
+        <v>25088</v>
       </c>
       <c r="B606">
         <v>1</v>
@@ -15067,7 +15489,7 @@
     </row>
     <row r="607" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A607">
-        <v>25319</v>
+        <v>25140</v>
       </c>
       <c r="B607">
         <v>1</v>
@@ -15075,274 +15497,274 @@
     </row>
     <row r="608" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A608">
-        <v>25088</v>
+        <v>25632</v>
       </c>
       <c r="B608">
         <v>1</v>
       </c>
     </row>
-    <row r="609" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="609" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A609">
-        <v>25140</v>
+        <v>24967</v>
       </c>
       <c r="B609">
         <v>1</v>
       </c>
     </row>
-    <row r="610" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="610" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A610">
-        <v>25632</v>
+        <v>24937</v>
       </c>
       <c r="B610">
         <v>1</v>
       </c>
     </row>
-    <row r="611" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="611" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A611">
-        <v>24967</v>
+        <v>25163</v>
       </c>
       <c r="B611">
         <v>1</v>
       </c>
     </row>
-    <row r="612" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="612" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A612">
-        <v>24937</v>
+        <v>25032</v>
       </c>
       <c r="B612">
         <v>1</v>
       </c>
     </row>
-    <row r="613" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="613" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A613">
-        <v>25163</v>
-      </c>
-      <c r="B613">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="614" spans="1:5" x14ac:dyDescent="0.25">
+        <v>16819</v>
+      </c>
+      <c r="E613" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="614" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A614">
-        <v>25032</v>
+        <v>15664</v>
       </c>
       <c r="B614">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="615" spans="1:5" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+      <c r="E614" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="615" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A615">
-        <v>16819</v>
+        <v>185165</v>
       </c>
       <c r="E615" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="616" spans="1:5" x14ac:dyDescent="0.25">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="616" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A616">
-        <v>15664</v>
+        <v>29236</v>
       </c>
       <c r="B616">
-        <v>0</v>
-      </c>
-      <c r="E616" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="617" spans="1:5" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="617" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A617">
-        <v>185165</v>
-      </c>
-      <c r="E617" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="618" spans="1:5" x14ac:dyDescent="0.25">
+        <v>29234</v>
+      </c>
+      <c r="B617">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="618" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A618">
-        <v>29236</v>
+        <v>29235</v>
       </c>
       <c r="B618">
         <v>1</v>
       </c>
     </row>
-    <row r="619" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="619" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A619">
-        <v>29234</v>
+        <v>29233</v>
       </c>
       <c r="B619">
         <v>1</v>
       </c>
     </row>
-    <row r="620" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="620" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A620">
-        <v>29235</v>
-      </c>
-      <c r="B620">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="621" spans="1:5" x14ac:dyDescent="0.25">
+        <v>19489</v>
+      </c>
+      <c r="E620" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="621" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A621">
-        <v>29233</v>
-      </c>
-      <c r="B621">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="622" spans="1:5" x14ac:dyDescent="0.25">
+        <v>17446</v>
+      </c>
+      <c r="E621" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="622" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A622">
-        <v>19489</v>
-      </c>
-      <c r="E622" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="623" spans="1:5" x14ac:dyDescent="0.25">
+        <v>24734</v>
+      </c>
+      <c r="B622">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="623" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A623">
-        <v>17446</v>
-      </c>
-      <c r="E623" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="624" spans="1:5" x14ac:dyDescent="0.25">
+        <v>3702</v>
+      </c>
+      <c r="H623" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="624" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A624">
-        <v>24734</v>
+        <v>23892</v>
       </c>
       <c r="B624">
         <v>1</v>
       </c>
     </row>
-    <row r="625" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="625" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A625">
-        <v>3702</v>
-      </c>
-      <c r="H625" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="626" spans="1:8" x14ac:dyDescent="0.25">
+        <v>23896</v>
+      </c>
+      <c r="B625">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="626" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A626">
-        <v>23892</v>
+        <v>23949</v>
       </c>
       <c r="B626">
         <v>1</v>
       </c>
     </row>
-    <row r="627" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="627" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A627">
-        <v>23896</v>
-      </c>
-      <c r="B627">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="628" spans="1:8" x14ac:dyDescent="0.25">
+        <v>142345</v>
+      </c>
+      <c r="E627" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="628" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A628">
-        <v>23949</v>
-      </c>
-      <c r="B628">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="629" spans="1:8" x14ac:dyDescent="0.25">
+        <v>142475</v>
+      </c>
+      <c r="E628" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="629" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A629">
-        <v>142345</v>
+        <v>142476</v>
       </c>
       <c r="E629" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="630" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="630" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A630">
-        <v>142475</v>
+        <v>142696</v>
       </c>
       <c r="E630" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="631" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="631" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A631">
-        <v>142476</v>
+        <v>1776</v>
       </c>
       <c r="E631" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="632" spans="1:8" x14ac:dyDescent="0.25">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="632" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A632">
-        <v>142696</v>
-      </c>
-      <c r="E632" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="633" spans="1:8" x14ac:dyDescent="0.25">
+        <v>23797</v>
+      </c>
+      <c r="B632">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="633" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A633">
-        <v>1776</v>
-      </c>
-      <c r="E633" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="634" spans="1:8" x14ac:dyDescent="0.25">
+        <v>23777</v>
+      </c>
+      <c r="B633">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="634" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A634">
-        <v>23797</v>
-      </c>
-      <c r="B634">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="635" spans="1:8" x14ac:dyDescent="0.25">
+        <v>37554</v>
+      </c>
+      <c r="E634" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="635" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A635">
-        <v>23777</v>
-      </c>
-      <c r="B635">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="636" spans="1:8" x14ac:dyDescent="0.25">
+        <v>6491</v>
+      </c>
+      <c r="E635" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="636" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A636">
-        <v>37554</v>
+        <v>29259</v>
       </c>
       <c r="E636" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="637" spans="1:8" x14ac:dyDescent="0.25">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="637" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A637">
-        <v>6491</v>
-      </c>
-      <c r="E637" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="638" spans="1:8" x14ac:dyDescent="0.25">
+        <v>16227</v>
+      </c>
+      <c r="B637">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="638" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A638">
-        <v>29259</v>
-      </c>
-      <c r="E638" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="639" spans="1:8" x14ac:dyDescent="0.25">
+        <v>28126</v>
+      </c>
+      <c r="B638">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="639" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A639">
-        <v>16227</v>
+        <v>16458</v>
       </c>
       <c r="B639">
         <v>0</v>
       </c>
     </row>
-    <row r="640" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="640" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A640">
-        <v>28126</v>
+        <v>15549</v>
       </c>
       <c r="B640">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="641" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A641">
-        <v>16458</v>
+        <v>15556</v>
       </c>
       <c r="B641">
         <v>0</v>
@@ -15350,7 +15772,7 @@
     </row>
     <row r="642" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A642">
-        <v>15549</v>
+        <v>15557</v>
       </c>
       <c r="B642">
         <v>0</v>
@@ -15358,7 +15780,7 @@
     </row>
     <row r="643" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A643">
-        <v>15556</v>
+        <v>15558</v>
       </c>
       <c r="B643">
         <v>0</v>
@@ -15366,7 +15788,7 @@
     </row>
     <row r="644" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A644">
-        <v>15557</v>
+        <v>15559</v>
       </c>
       <c r="B644">
         <v>0</v>
@@ -15374,7 +15796,7 @@
     </row>
     <row r="645" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A645">
-        <v>15558</v>
+        <v>15560</v>
       </c>
       <c r="B645">
         <v>0</v>
@@ -15382,7 +15804,7 @@
     </row>
     <row r="646" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A646">
-        <v>15559</v>
+        <v>15561</v>
       </c>
       <c r="B646">
         <v>0</v>
@@ -15390,7 +15812,7 @@
     </row>
     <row r="647" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A647">
-        <v>15560</v>
+        <v>15562</v>
       </c>
       <c r="B647">
         <v>0</v>
@@ -15398,7 +15820,7 @@
     </row>
     <row r="648" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A648">
-        <v>15561</v>
+        <v>15563</v>
       </c>
       <c r="B648">
         <v>0</v>
@@ -15406,7 +15828,7 @@
     </row>
     <row r="649" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A649">
-        <v>15562</v>
+        <v>15564</v>
       </c>
       <c r="B649">
         <v>0</v>
@@ -15414,7 +15836,7 @@
     </row>
     <row r="650" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A650">
-        <v>15563</v>
+        <v>15565</v>
       </c>
       <c r="B650">
         <v>0</v>
@@ -15422,7 +15844,7 @@
     </row>
     <row r="651" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A651">
-        <v>15564</v>
+        <v>15566</v>
       </c>
       <c r="B651">
         <v>0</v>
@@ -15430,7 +15852,7 @@
     </row>
     <row r="652" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A652">
-        <v>15565</v>
+        <v>15567</v>
       </c>
       <c r="B652">
         <v>0</v>
@@ -15438,7 +15860,7 @@
     </row>
     <row r="653" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A653">
-        <v>15566</v>
+        <v>15568</v>
       </c>
       <c r="B653">
         <v>0</v>
@@ -15446,7 +15868,7 @@
     </row>
     <row r="654" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A654">
-        <v>15567</v>
+        <v>15569</v>
       </c>
       <c r="B654">
         <v>0</v>
@@ -15454,7 +15876,7 @@
     </row>
     <row r="655" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A655">
-        <v>15568</v>
+        <v>15570</v>
       </c>
       <c r="B655">
         <v>0</v>
@@ -15462,7 +15884,7 @@
     </row>
     <row r="656" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A656">
-        <v>15569</v>
+        <v>15572</v>
       </c>
       <c r="B656">
         <v>0</v>
@@ -15470,7 +15892,7 @@
     </row>
     <row r="657" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A657">
-        <v>15570</v>
+        <v>15573</v>
       </c>
       <c r="B657">
         <v>0</v>
@@ -15478,7 +15900,7 @@
     </row>
     <row r="658" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A658">
-        <v>15572</v>
+        <v>15574</v>
       </c>
       <c r="B658">
         <v>0</v>
@@ -15486,7 +15908,7 @@
     </row>
     <row r="659" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A659">
-        <v>15573</v>
+        <v>15575</v>
       </c>
       <c r="B659">
         <v>0</v>
@@ -15494,7 +15916,7 @@
     </row>
     <row r="660" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A660">
-        <v>15574</v>
+        <v>15576</v>
       </c>
       <c r="B660">
         <v>0</v>
@@ -15502,7 +15924,7 @@
     </row>
     <row r="661" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A661">
-        <v>15575</v>
+        <v>15577</v>
       </c>
       <c r="B661">
         <v>0</v>
@@ -15510,7 +15932,7 @@
     </row>
     <row r="662" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A662">
-        <v>15576</v>
+        <v>15578</v>
       </c>
       <c r="B662">
         <v>0</v>
@@ -15518,7 +15940,7 @@
     </row>
     <row r="663" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A663">
-        <v>15577</v>
+        <v>15579</v>
       </c>
       <c r="B663">
         <v>0</v>
@@ -15526,7 +15948,7 @@
     </row>
     <row r="664" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A664">
-        <v>15578</v>
+        <v>15581</v>
       </c>
       <c r="B664">
         <v>0</v>
@@ -15534,7 +15956,7 @@
     </row>
     <row r="665" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A665">
-        <v>15579</v>
+        <v>15582</v>
       </c>
       <c r="B665">
         <v>0</v>
@@ -15542,7 +15964,7 @@
     </row>
     <row r="666" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A666">
-        <v>15581</v>
+        <v>15583</v>
       </c>
       <c r="B666">
         <v>0</v>
@@ -15550,7 +15972,7 @@
     </row>
     <row r="667" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A667">
-        <v>15582</v>
+        <v>15584</v>
       </c>
       <c r="B667">
         <v>0</v>
@@ -15558,7 +15980,7 @@
     </row>
     <row r="668" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A668">
-        <v>15583</v>
+        <v>15585</v>
       </c>
       <c r="B668">
         <v>0</v>
@@ -15566,7 +15988,7 @@
     </row>
     <row r="669" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A669">
-        <v>15584</v>
+        <v>15586</v>
       </c>
       <c r="B669">
         <v>0</v>
@@ -15574,7 +15996,7 @@
     </row>
     <row r="670" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A670">
-        <v>15585</v>
+        <v>15587</v>
       </c>
       <c r="B670">
         <v>0</v>
@@ -15582,7 +16004,7 @@
     </row>
     <row r="671" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A671">
-        <v>15586</v>
+        <v>15588</v>
       </c>
       <c r="B671">
         <v>0</v>
@@ -15590,7 +16012,7 @@
     </row>
     <row r="672" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A672">
-        <v>15587</v>
+        <v>15592</v>
       </c>
       <c r="B672">
         <v>0</v>
@@ -15598,7 +16020,7 @@
     </row>
     <row r="673" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A673">
-        <v>15588</v>
+        <v>15593</v>
       </c>
       <c r="B673">
         <v>0</v>
@@ -15606,7 +16028,7 @@
     </row>
     <row r="674" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A674">
-        <v>15592</v>
+        <v>15594</v>
       </c>
       <c r="B674">
         <v>0</v>
@@ -15614,7 +16036,7 @@
     </row>
     <row r="675" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A675">
-        <v>15593</v>
+        <v>15595</v>
       </c>
       <c r="B675">
         <v>0</v>
@@ -15622,7 +16044,7 @@
     </row>
     <row r="676" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A676">
-        <v>15594</v>
+        <v>15596</v>
       </c>
       <c r="B676">
         <v>0</v>
@@ -15630,7 +16052,7 @@
     </row>
     <row r="677" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A677">
-        <v>15595</v>
+        <v>15597</v>
       </c>
       <c r="B677">
         <v>0</v>
@@ -15638,7 +16060,7 @@
     </row>
     <row r="678" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A678">
-        <v>15596</v>
+        <v>15598</v>
       </c>
       <c r="B678">
         <v>0</v>
@@ -15646,7 +16068,7 @@
     </row>
     <row r="679" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A679">
-        <v>15597</v>
+        <v>15599</v>
       </c>
       <c r="B679">
         <v>0</v>
@@ -15654,7 +16076,7 @@
     </row>
     <row r="680" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A680">
-        <v>15598</v>
+        <v>15600</v>
       </c>
       <c r="B680">
         <v>0</v>
@@ -15662,7 +16084,7 @@
     </row>
     <row r="681" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A681">
-        <v>15599</v>
+        <v>15601</v>
       </c>
       <c r="B681">
         <v>0</v>
@@ -15670,7 +16092,7 @@
     </row>
     <row r="682" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A682">
-        <v>15600</v>
+        <v>15602</v>
       </c>
       <c r="B682">
         <v>0</v>
@@ -15678,7 +16100,7 @@
     </row>
     <row r="683" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A683">
-        <v>15601</v>
+        <v>15603</v>
       </c>
       <c r="B683">
         <v>0</v>
@@ -15686,7 +16108,7 @@
     </row>
     <row r="684" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A684">
-        <v>15602</v>
+        <v>15604</v>
       </c>
       <c r="B684">
         <v>0</v>
@@ -15694,7 +16116,7 @@
     </row>
     <row r="685" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A685">
-        <v>15603</v>
+        <v>15605</v>
       </c>
       <c r="B685">
         <v>0</v>
@@ -15702,7 +16124,7 @@
     </row>
     <row r="686" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A686">
-        <v>15604</v>
+        <v>15606</v>
       </c>
       <c r="B686">
         <v>0</v>
@@ -15710,7 +16132,7 @@
     </row>
     <row r="687" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A687">
-        <v>15605</v>
+        <v>15607</v>
       </c>
       <c r="B687">
         <v>0</v>
@@ -15718,7 +16140,7 @@
     </row>
     <row r="688" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A688">
-        <v>15606</v>
+        <v>15871</v>
       </c>
       <c r="B688">
         <v>0</v>
@@ -15726,7 +16148,7 @@
     </row>
     <row r="689" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A689">
-        <v>15607</v>
+        <v>15580</v>
       </c>
       <c r="B689">
         <v>0</v>
@@ -15734,7 +16156,7 @@
     </row>
     <row r="690" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A690">
-        <v>15871</v>
+        <v>15864</v>
       </c>
       <c r="B690">
         <v>0</v>
@@ -15742,55 +16164,55 @@
     </row>
     <row r="691" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A691">
-        <v>15580</v>
-      </c>
-      <c r="B691">
-        <v>0</v>
+        <v>14354</v>
+      </c>
+      <c r="E691" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="692" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A692">
-        <v>15864</v>
-      </c>
-      <c r="B692">
-        <v>0</v>
+        <v>9467</v>
+      </c>
+      <c r="E692" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="693" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A693">
-        <v>14354</v>
+        <v>1855</v>
       </c>
       <c r="E693" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
     </row>
     <row r="694" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A694">
-        <v>9467</v>
+        <v>12126</v>
       </c>
       <c r="E694" t="s">
-        <v>70</v>
+        <v>33</v>
       </c>
     </row>
     <row r="695" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A695">
-        <v>1855</v>
-      </c>
-      <c r="E695" t="s">
-        <v>33</v>
+        <v>16284</v>
+      </c>
+      <c r="B695">
+        <v>0</v>
       </c>
     </row>
     <row r="696" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A696">
-        <v>12126</v>
-      </c>
-      <c r="E696" t="s">
-        <v>33</v>
+        <v>16135</v>
+      </c>
+      <c r="B696">
+        <v>0</v>
       </c>
     </row>
     <row r="697" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A697">
-        <v>16284</v>
+        <v>16134</v>
       </c>
       <c r="B697">
         <v>0</v>
@@ -15798,7 +16220,7 @@
     </row>
     <row r="698" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A698">
-        <v>16135</v>
+        <v>16212</v>
       </c>
       <c r="B698">
         <v>0</v>
@@ -15806,7 +16228,7 @@
     </row>
     <row r="699" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A699">
-        <v>16134</v>
+        <v>16161</v>
       </c>
       <c r="B699">
         <v>0</v>
@@ -15814,7 +16236,7 @@
     </row>
     <row r="700" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A700">
-        <v>16212</v>
+        <v>16115</v>
       </c>
       <c r="B700">
         <v>0</v>
@@ -15822,7 +16244,7 @@
     </row>
     <row r="701" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A701">
-        <v>16161</v>
+        <v>16114</v>
       </c>
       <c r="B701">
         <v>0</v>
@@ -15830,7 +16252,7 @@
     </row>
     <row r="702" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A702">
-        <v>16115</v>
+        <v>16132</v>
       </c>
       <c r="B702">
         <v>0</v>
@@ -15838,7 +16260,7 @@
     </row>
     <row r="703" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A703">
-        <v>16114</v>
+        <v>16131</v>
       </c>
       <c r="B703">
         <v>0</v>
@@ -15846,7 +16268,7 @@
     </row>
     <row r="704" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A704">
-        <v>16132</v>
+        <v>16283</v>
       </c>
       <c r="B704">
         <v>0</v>
@@ -15854,7 +16276,7 @@
     </row>
     <row r="705" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A705">
-        <v>16131</v>
+        <v>17069</v>
       </c>
       <c r="B705">
         <v>0</v>
@@ -15862,7 +16284,7 @@
     </row>
     <row r="706" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A706">
-        <v>16283</v>
+        <v>17072</v>
       </c>
       <c r="B706">
         <v>0</v>
@@ -15870,23 +16292,23 @@
     </row>
     <row r="707" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A707">
-        <v>17069</v>
+        <v>25200</v>
       </c>
       <c r="B707">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="708" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A708">
-        <v>17072</v>
+        <v>25207</v>
       </c>
       <c r="B708">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="709" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A709">
-        <v>25200</v>
+        <v>23988</v>
       </c>
       <c r="B709">
         <v>1</v>
@@ -15894,7 +16316,7 @@
     </row>
     <row r="710" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A710">
-        <v>25207</v>
+        <v>28209</v>
       </c>
       <c r="B710">
         <v>1</v>
@@ -15902,7 +16324,7 @@
     </row>
     <row r="711" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A711">
-        <v>23988</v>
+        <v>25202</v>
       </c>
       <c r="B711">
         <v>1</v>
@@ -15910,7 +16332,7 @@
     </row>
     <row r="712" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A712">
-        <v>28209</v>
+        <v>28210</v>
       </c>
       <c r="B712">
         <v>1</v>
@@ -15918,143 +16340,143 @@
     </row>
     <row r="713" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A713">
-        <v>25202</v>
-      </c>
-      <c r="B713">
-        <v>1</v>
+        <v>23618</v>
+      </c>
+      <c r="E713" t="s">
+        <v>71</v>
       </c>
     </row>
     <row r="714" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A714">
-        <v>28210</v>
-      </c>
-      <c r="B714">
-        <v>1</v>
+        <v>30562</v>
+      </c>
+      <c r="E714" t="s">
+        <v>71</v>
       </c>
     </row>
     <row r="715" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A715">
-        <v>23618</v>
+        <v>28760</v>
       </c>
       <c r="E715" t="s">
-        <v>72</v>
+        <v>31</v>
       </c>
     </row>
     <row r="716" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A716">
-        <v>30562</v>
+        <v>28500</v>
       </c>
       <c r="E716" t="s">
-        <v>72</v>
+        <v>43</v>
       </c>
     </row>
     <row r="717" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A717">
-        <v>28760</v>
+        <v>28471</v>
       </c>
       <c r="E717" t="s">
-        <v>31</v>
+        <v>74</v>
       </c>
     </row>
     <row r="718" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A718">
-        <v>28500</v>
+        <v>29195</v>
       </c>
       <c r="E718" t="s">
-        <v>43</v>
+        <v>74</v>
       </c>
     </row>
     <row r="719" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A719">
-        <v>28471</v>
+        <v>29196</v>
       </c>
       <c r="E719" t="s">
-        <v>75</v>
+        <v>63</v>
       </c>
     </row>
     <row r="720" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A720">
-        <v>29195</v>
+        <v>28474</v>
       </c>
       <c r="E720" t="s">
-        <v>75</v>
+        <v>84</v>
       </c>
     </row>
     <row r="721" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A721">
-        <v>29196</v>
+        <v>29194</v>
       </c>
       <c r="E721" t="s">
-        <v>63</v>
+        <v>84</v>
       </c>
     </row>
     <row r="722" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A722">
-        <v>28474</v>
-      </c>
-      <c r="E722" t="s">
-        <v>85</v>
+        <v>23951</v>
+      </c>
+      <c r="B722">
+        <v>1</v>
       </c>
     </row>
     <row r="723" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A723">
-        <v>29194</v>
-      </c>
-      <c r="E723" t="s">
-        <v>85</v>
+        <v>50961</v>
+      </c>
+      <c r="B723">
+        <v>0</v>
       </c>
     </row>
     <row r="724" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A724">
-        <v>23951</v>
-      </c>
-      <c r="B724">
-        <v>1</v>
+        <v>17468</v>
+      </c>
+      <c r="E724" t="s">
+        <v>131</v>
       </c>
     </row>
     <row r="725" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A725">
-        <v>50961</v>
-      </c>
-      <c r="B725">
-        <v>0</v>
+        <v>24208</v>
+      </c>
+      <c r="E725" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="726" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A726">
-        <v>17468</v>
+        <v>28908</v>
       </c>
       <c r="E726" t="s">
-        <v>132</v>
+        <v>63</v>
       </c>
     </row>
     <row r="727" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A727">
-        <v>24208</v>
+        <v>28943</v>
       </c>
       <c r="E727" t="s">
-        <v>11</v>
+        <v>31</v>
       </c>
     </row>
     <row r="728" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A728">
-        <v>28908</v>
-      </c>
-      <c r="E728" t="s">
-        <v>63</v>
+        <v>23995</v>
+      </c>
+      <c r="B728">
+        <v>1</v>
       </c>
     </row>
     <row r="729" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A729">
-        <v>28943</v>
-      </c>
-      <c r="E729" t="s">
-        <v>31</v>
+        <v>29590</v>
+      </c>
+      <c r="B729">
+        <v>1</v>
       </c>
     </row>
     <row r="730" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A730">
-        <v>23995</v>
+        <v>28552</v>
       </c>
       <c r="B730">
         <v>1</v>
@@ -16062,7 +16484,7 @@
     </row>
     <row r="731" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A731">
-        <v>29590</v>
+        <v>24975</v>
       </c>
       <c r="B731">
         <v>1</v>
@@ -16070,38 +16492,105 @@
     </row>
     <row r="732" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A732">
-        <v>28552</v>
-      </c>
-      <c r="B732">
-        <v>1</v>
+        <v>18063</v>
+      </c>
+      <c r="E732" t="s">
+        <v>133</v>
       </c>
     </row>
     <row r="733" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A733">
-        <v>24975</v>
-      </c>
-      <c r="B733">
-        <v>1</v>
+        <v>25237</v>
+      </c>
+      <c r="E733" t="s">
+        <v>133</v>
       </c>
     </row>
     <row r="734" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A734">
-        <v>18063</v>
+        <v>39372</v>
       </c>
       <c r="E734" t="s">
-        <v>134</v>
+        <v>133</v>
+      </c>
+    </row>
+    <row r="735" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A735">
+        <v>23897</v>
+      </c>
+      <c r="B735">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="736" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A736">
+        <v>23761</v>
+      </c>
+      <c r="B736">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="737" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A737">
+        <v>18165</v>
+      </c>
+      <c r="E737" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="738" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A738">
+        <v>16814</v>
+      </c>
+      <c r="E738" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="739" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A739">
+        <v>32405</v>
+      </c>
+      <c r="B739">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="740" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A740">
+        <v>25272</v>
+      </c>
+      <c r="E740" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="741" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A741">
+        <v>187565</v>
+      </c>
+      <c r="E741" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="742" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A742">
+        <v>25198</v>
+      </c>
+      <c r="E742" t="s">
+        <v>166</v>
       </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1">
-    <cfRule type="duplicateValues" dxfId="3" priority="1"/>
-    <cfRule type="duplicateValues" dxfId="2" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="3"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A2:A501 A503:A650">
-    <cfRule type="duplicateValues" dxfId="1" priority="92"/>
+  <conditionalFormatting sqref="A1:A1048576">
+    <cfRule type="duplicateValues" dxfId="2" priority="1"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A2:A650">
-    <cfRule type="duplicateValues" dxfId="0" priority="95"/>
+  <conditionalFormatting sqref="A2:A648">
+    <cfRule type="duplicateValues" dxfId="1" priority="106"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A502:A648 A2:A500">
+    <cfRule type="duplicateValues" dxfId="0" priority="100"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
